--- a/2026/SALTA 1167/Mayo/SALTA1167-Mayo.xlsx
+++ b/2026/SALTA 1167/Mayo/SALTA1167-Mayo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C726E264-7C1F-478D-BF7B-FBCEEA05B61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38AC16E-EA39-49B9-A52B-4AAADCAAD06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,19 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="148">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -395,9 +400,6 @@
   </si>
   <si>
     <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 1-2249124-0</t>
-  </si>
-  <si>
-    <t>Subidos en en3r0</t>
   </si>
   <si>
     <t>REITERAMOS QUE LOS DATOS DE LA CUENTA EN DONDE DEBEN ABONAR LAS EXPENSAS SON: CONSORCIO DE PROPIETARIOS EDIFICIO CALLE SALTA 1167/1169  - C DE P SALTA 1167 1169 LANUS - CTA CTE $   039 - 22273/6   CBU: 0720039720000002227368</t>
@@ -417,39 +419,6 @@
     <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE SALTA 1167</t>
   </si>
   <si>
-    <t>Transf 24/04</t>
-  </si>
-  <si>
-    <t>Sagitario pintureria - Recubrick Ceramico</t>
-  </si>
-  <si>
-    <t>Transf 06/04</t>
-  </si>
-  <si>
-    <t>Pintureria Indugar - Recuplast, pulso de colorante C, B e I</t>
-  </si>
-  <si>
-    <t>Debito 06/04</t>
-  </si>
-  <si>
-    <t>De Maio Hector - Mantenimiento piscina y reparacion caño bomba</t>
-  </si>
-  <si>
-    <t>Arreglo de porton - Sr. Herrero</t>
-  </si>
-  <si>
-    <t>Transf 16/04</t>
-  </si>
-  <si>
-    <t>Transf 30/04</t>
-  </si>
-  <si>
-    <t>Pricemania compra de cajita portallave</t>
-  </si>
-  <si>
-    <t>Transf 17/04</t>
-  </si>
-  <si>
     <t>Federacion patronal - Seguro silleteros</t>
   </si>
   <si>
@@ -459,18 +428,9 @@
     <t xml:space="preserve">Bonificado x EDESUR </t>
   </si>
   <si>
-    <t>Honorarios administracion - Mes anterior</t>
-  </si>
-  <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
     <t>SUM</t>
   </si>
   <si>
-    <t>Easy Barracas - Compra de termotanque - Cuota 2  - Restan 4 cuotas de $157.988,29</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
@@ -490,6 +450,36 @@
   </si>
   <si>
     <t>Recarga de matafuegos</t>
+  </si>
+  <si>
+    <t>Transf 05/05</t>
+  </si>
+  <si>
+    <t>Debito 06/05</t>
+  </si>
+  <si>
+    <t>Pintor - Sr. Gabriel - Trabajo en medianeras</t>
+  </si>
+  <si>
+    <t>Transf 07/05</t>
+  </si>
+  <si>
+    <t>Sr. Herrero - Tacho de basura</t>
+  </si>
+  <si>
+    <t>Transf 18/05</t>
+  </si>
+  <si>
+    <t>Lema - Ascensores - Alineacion cabina de ascensores (se desmontan los rodillos, se limpian, se egrasan, retiran y se vuelven a colocar alineadas las cuneas para no ocasionar mas ruido con la cabina al deslizarse desnivelada)</t>
+  </si>
+  <si>
+    <t>Transf 27/05</t>
+  </si>
+  <si>
+    <t>Easy Barracas - Compra de termotanque - Cuota 3  - Restan 3 cuotas de $157.988,29</t>
+  </si>
+  <si>
+    <t>Transf 29/05</t>
   </si>
 </sst>
 </file>
@@ -508,7 +498,7 @@
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,13 +686,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <u/>
@@ -1141,7 +1124,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1343,9 +1326,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1356,9 +1336,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1434,7 +1411,7 @@
     <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1447,139 +1424,149 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1658,9 +1645,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1698,9 +1685,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1733,9 +1720,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1768,9 +1772,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1944,22 +1965,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="50" t="s">
         <v>74</v>
@@ -1968,7 +1989,7 @@
       <c r="D1" s="50"/>
       <c r="E1" s="51"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="52" t="s">
         <v>14</v>
@@ -1977,16 +1998,16 @@
       <c r="D2" s="52"/>
       <c r="E2" s="53"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="194" t="s">
+      <c r="B3" s="199" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="195"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="200"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -1997,12 +2018,12 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>75</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="52" t="s">
@@ -2010,68 +2031,68 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="197" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="197"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="197"/>
-      <c r="C10" s="197"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="196" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="202" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="202"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="202"/>
+      <c r="C9" s="202"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="202"/>
+      <c r="C10" s="202"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="201" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="196"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="196"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="196"/>
-      <c r="B14" s="196"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="196"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="196"/>
-      <c r="B15" s="196"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
-      <c r="E15" s="196"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="196"/>
-      <c r="B16" s="196"/>
-      <c r="C16" s="196"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="196"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="201"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="201"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="201"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="201"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="201"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="201"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>104</v>
       </c>
@@ -2080,7 +2101,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>77</v>
       </c>
@@ -2089,76 +2110,76 @@
       <c r="D21" s="109"/>
       <c r="E21" s="100"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="192" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="197" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="193"/>
+      <c r="B22" s="198"/>
       <c r="C22" s="38"/>
-      <c r="D22" s="232">
+      <c r="D22" s="187">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="183" t="s">
-        <v>150</v>
+      <c r="E22" s="181" t="s">
+        <v>135</v>
       </c>
       <c r="H22" s="89"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="192"/>
-      <c r="B23" s="193"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="197"/>
+      <c r="B23" s="198"/>
       <c r="C23" s="38"/>
       <c r="D23" s="110"/>
       <c r="E23" s="103"/>
       <c r="H23" s="89"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
       <c r="D24" s="111"/>
-      <c r="E24" s="173">
+      <c r="E24" s="171">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="112"/>
-      <c r="E25" s="174"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="192" t="s">
+      <c r="E25" s="172"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="197" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="193"/>
+      <c r="B26" s="198"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="187">
+      <c r="D26" s="189">
         <v>75267</v>
       </c>
-      <c r="E26" s="172" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="170" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="121" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B27" s="122"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="188">
+      <c r="D27" s="185">
         <v>29150</v>
       </c>
-      <c r="E27" s="172" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E27" s="170" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
         <v>1</v>
       </c>
@@ -2170,16 +2191,16 @@
         <v>104417</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>10</v>
       </c>
       <c r="B29" s="101"/>
       <c r="C29" s="101"/>
       <c r="D29" s="113"/>
-      <c r="E29" s="175"/>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="173"/>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>67</v>
       </c>
@@ -2188,649 +2209,612 @@
       <c r="D30" s="104">
         <v>0</v>
       </c>
-      <c r="E30" s="183"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E30" s="181"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="231">
+      <c r="D31" s="186">
         <v>6420.51</v>
       </c>
-      <c r="E31" s="183" t="str">
+      <c r="E31" s="181" t="str">
         <f>E32</f>
-        <v>Transf 06/04</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>Transf 05/05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B32" s="120"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="231">
+      <c r="D32" s="186">
         <v>330512.58</v>
       </c>
       <c r="E32" s="105" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="190" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="191"/>
+      <c r="B33" s="196"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="104">
+      <c r="D33" s="186">
         <v>193996.95</v>
       </c>
       <c r="E33" s="105" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="106" t="s">
         <v>78</v>
       </c>
       <c r="B34" s="102"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="104">
-        <v>23979.77</v>
+      <c r="D34" s="186">
+        <v>24915.01</v>
       </c>
       <c r="E34" s="105" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="114"/>
-      <c r="E35" s="176">
+      <c r="E35" s="174">
         <f>SUM(D30:D34)</f>
-        <v>554909.81000000006</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>555845.05000000005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25"/>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="111"/>
-      <c r="E36" s="177"/>
-    </row>
-    <row r="37" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="192" t="s">
+      <c r="E36" s="175"/>
+    </row>
+    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="197" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="193"/>
+      <c r="B37" s="198"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="231">
+      <c r="D37" s="186">
         <v>82000</v>
       </c>
       <c r="E37" s="105" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="182" t="s">
-        <v>131</v>
-      </c>
-      <c r="B38" s="122"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="197" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="198"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="74">
-        <v>73711</v>
+      <c r="D38" s="188">
+        <v>300000</v>
       </c>
       <c r="E38" s="105" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="192" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="193"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="180" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="122"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="233">
+      <c r="D39" s="188">
+        <v>900000</v>
+      </c>
+      <c r="E39" s="105" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="197" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" s="198"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="188">
         <v>148155</v>
       </c>
-      <c r="E39" s="105" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="121" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="122"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="74">
-        <v>84133</v>
-      </c>
       <c r="E40" s="105" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="121" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B41" s="122"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="74">
-        <v>13394</v>
+      <c r="D41" s="188">
+        <v>120000</v>
       </c>
       <c r="E41" s="105" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="121" t="s">
-        <v>134</v>
-      </c>
-      <c r="B42" s="122"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="197" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" s="198"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="74">
-        <v>48900</v>
-      </c>
-      <c r="E42" s="105" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="192" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="193"/>
+      <c r="D42" s="188">
+        <v>157988.29</v>
+      </c>
+      <c r="E42" s="105"/>
+    </row>
+    <row r="43" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="197"/>
+      <c r="B43" s="198"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="74">
-        <v>157988.29</v>
-      </c>
+      <c r="D43" s="74"/>
       <c r="E43" s="105"/>
     </row>
-    <row r="44" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="192" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44" s="193"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="74">
-        <v>30000</v>
-      </c>
-      <c r="E44" s="105" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>6</v>
+      </c>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="123">
+        <f>SUM(D37:D43)</f>
+        <v>1708143.29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>11</v>
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="123">
-        <f>SUM(D37:D44)</f>
-        <v>638281.29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="109"/>
-      <c r="E46" s="178"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="192" t="s">
-        <v>142</v>
-      </c>
-      <c r="B47" s="193"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="110">
+      <c r="D45" s="109"/>
+      <c r="E45" s="176"/>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="122"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="190">
         <v>150000</v>
       </c>
-      <c r="E47" s="179"/>
-      <c r="G47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="121" t="s">
-        <v>149</v>
-      </c>
-      <c r="B48" s="122"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="189">
+      <c r="E46" s="177" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="171">
+        <f>SUM(D46:D46)</f>
         <v>150000</v>
       </c>
-      <c r="E48" s="179" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="21" t="s">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="48"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="123"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="191">
+        <v>0</v>
+      </c>
+      <c r="E49" s="178"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="191">
+        <v>0</v>
+      </c>
+      <c r="E50" s="179"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="173">
-        <f>SUM(D47:D48)</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="48"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="108"/>
-      <c r="E50" s="123"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="104">
-        <v>0</v>
-      </c>
-      <c r="E51" s="180"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>116</v>
-      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="123">
+        <f>SUM(D49:D50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="104">
-        <f>2585+28980.86</f>
-        <v>31565.86</v>
-      </c>
-      <c r="E52" s="181"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="76"/>
-      <c r="E53" s="123">
-        <f>SUM(D51:D52)</f>
-        <v>31565.86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="77"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="22" t="s">
+      <c r="D52" s="71"/>
+      <c r="E52" s="77"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="78"/>
-      <c r="E55" s="124">
-        <f>(2200000)-1314557.42-60000-39.8</f>
-        <v>825402.78</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="124"/>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="30"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="8"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="82">
+        <f>(SUM(E21:E53))</f>
+        <v>3029252.19</v>
+      </c>
+      <c r="F55" s="99"/>
+      <c r="G55" s="30"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D56" s="79"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="30"/>
-    </row>
-    <row r="57" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="81"/>
-      <c r="E57" s="82">
-        <f>(SUM(E21:E55))</f>
-        <v>2965423.59</v>
-      </c>
-      <c r="F57" s="99"/>
-      <c r="G57" s="30"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
-    </row>
-    <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
-      <c r="H59" s="115"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="s">
+      <c r="E56" s="79"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="79"/>
+      <c r="E57" s="79"/>
+      <c r="H57" s="115"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B60" s="10"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="84"/>
-    </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="73"/>
-      <c r="B61" s="102"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="84"/>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="73"/>
+      <c r="B59" s="102"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="72"/>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="205"/>
+      <c r="B60" s="205"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="72"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="72"/>
-    </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="200"/>
-      <c r="B62" s="200"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="73"/>
+      <c r="B62" s="75"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="104"/>
+      <c r="D62" s="74"/>
       <c r="E62" s="72"/>
     </row>
-    <row r="63" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="73"/>
-      <c r="B64" s="75"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="74"/>
-      <c r="E64" s="72"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="35"/>
-      <c r="B65" s="34"/>
-      <c r="C65" s="34"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41">
-        <f>SUM(D61:D64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="22" t="s">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="35"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41">
+        <f>SUM(D59:D62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="169"/>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="23"/>
+      <c r="E66" s="167"/>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="49">
-        <f>E65+E68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="8"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="49">
+        <f>E63+E66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="70">
+        <f>E55</f>
+        <v>3029252.19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" s="70">
+        <f>E55-E53</f>
+        <v>3029252.19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="69" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B72" s="70">
-        <f>E57</f>
-        <v>2965423.59</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E68-E66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="69" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B73" s="70">
-        <f>E57-E55</f>
-        <v>2140020.8099999996</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="B74" s="70">
-        <f>E70-E68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="B75" s="70">
-        <f>E70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="27"/>
-    </row>
-    <row r="78" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="91" t="s">
+        <f>E68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="27"/>
+    </row>
+    <row r="76" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="91" t="s">
         <v>109</v>
       </c>
-      <c r="B78" s="136">
-        <v>577835.94999999995</v>
-      </c>
-      <c r="C78" s="27"/>
-      <c r="D78" s="33"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B76" s="134">
+        <v>956980.3900000006</v>
+      </c>
+      <c r="C76" s="27"/>
+      <c r="D76" s="33"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" s="96">
+        <f>-B71</f>
+        <v>-3029252.19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" s="96">
+        <f>B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="B79" s="96">
-        <f>-B73</f>
-        <v>-2140020.8099999996</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" s="97">
+        <f>PRORRATEO!G36-B86</f>
+        <v>2504691.1700000009</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="98" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" s="116"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" s="95">
+        <f>SUM(B76:C80)</f>
+        <v>432419.37000000151</v>
+      </c>
+      <c r="D81" s="30"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="92"/>
+      <c r="B82" s="92"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="29"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="91" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" s="134">
+        <v>2000000</v>
+      </c>
+      <c r="D83" s="29"/>
+      <c r="E83" s="30"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B84" s="96">
+        <f>-B72</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B80" s="96">
-        <f>B98</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="B81" s="97">
-        <f>PRORRATEO!G36-B88</f>
-        <v>2409066.1000000006</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="98" t="s">
+      <c r="B85" s="96">
+        <f>B104</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="30"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" s="97">
+        <v>0</v>
+      </c>
+      <c r="D86" s="168" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="116"/>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="B83" s="95">
-        <f>SUM(B78:C82)</f>
-        <v>846881.24000000092</v>
-      </c>
-      <c r="D83" s="30"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="92"/>
-      <c r="B84" s="92"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="29"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="91" t="s">
-        <v>110</v>
-      </c>
-      <c r="B85" s="136">
+      <c r="B87" s="116"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B88" s="95">
+        <f>SUM(B83:C87)</f>
         <v>2000000</v>
       </c>
-      <c r="D85" s="29"/>
-      <c r="E85" s="30"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B86" s="96">
-        <f>-B74</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B87" s="96">
-        <f>B106</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="30"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="B88" s="97">
-        <v>0</v>
-      </c>
-      <c r="D88" s="170" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="98" t="s">
-        <v>24</v>
-      </c>
-      <c r="B89" s="116"/>
-    </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="B90" s="95">
-        <f>SUM(B85:C89)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="92"/>
-      <c r="B91" s="92"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="92"/>
-      <c r="B92" s="92"/>
-    </row>
-    <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="199" t="s">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="92"/>
+      <c r="B89" s="92"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="92"/>
+      <c r="B90" s="92"/>
+    </row>
+    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="199"/>
-      <c r="C94" s="199"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="199"/>
-      <c r="B95" s="199"/>
-      <c r="C95" s="199"/>
-    </row>
-    <row r="96" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="86"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26">
+      <c r="B92" s="204"/>
+      <c r="C92" s="204"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="204"/>
+      <c r="B93" s="204"/>
+      <c r="C93" s="204"/>
+    </row>
+    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="86"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="26">
         <v>40000</v>
       </c>
-      <c r="E96" s="99"/>
-    </row>
-    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="86"/>
-      <c r="B97" s="88"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="99"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A98" s="31" t="s">
+      <c r="E94" s="99"/>
+    </row>
+    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="86"/>
+      <c r="B95" s="88"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="99"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B98" s="87">
-        <f>SUM(B96:B97)</f>
-        <v>0</v>
-      </c>
-      <c r="C98" s="32"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M99" s="6"/>
-    </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="198"/>
-      <c r="B100" s="198"/>
-      <c r="C100" s="198"/>
-      <c r="D100" s="198"/>
-      <c r="E100" s="198"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="198"/>
-      <c r="B101" s="198"/>
-      <c r="C101" s="198"/>
-      <c r="D101" s="198"/>
-      <c r="E101" s="198"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="198"/>
-      <c r="B102" s="198"/>
-      <c r="C102" s="198"/>
-      <c r="D102" s="198"/>
-      <c r="E102" s="198"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="198"/>
-      <c r="B103" s="198"/>
-      <c r="C103" s="198"/>
-      <c r="D103" s="198"/>
-      <c r="E103" s="198"/>
+      <c r="B96" s="87">
+        <f>SUM(B94:B95)</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="32"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M97" s="6"/>
+    </row>
+    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="203"/>
+      <c r="B98" s="203"/>
+      <c r="C98" s="203"/>
+      <c r="D98" s="203"/>
+      <c r="E98" s="203"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="203"/>
+      <c r="B99" s="203"/>
+      <c r="C99" s="203"/>
+      <c r="D99" s="203"/>
+      <c r="E99" s="203"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="203"/>
+      <c r="B100" s="203"/>
+      <c r="C100" s="203"/>
+      <c r="D100" s="203"/>
+      <c r="E100" s="203"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="203"/>
+      <c r="B101" s="203"/>
+      <c r="C101" s="203"/>
+      <c r="D101" s="203"/>
+      <c r="E101" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A100:E103"/>
-    <mergeCell ref="A94:C95"/>
-    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A98:E101"/>
+    <mergeCell ref="A92:C93"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2848,298 +2832,298 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="137"/>
-      <c r="B1" s="138"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="140"/>
-    </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="141"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144" t="s">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="135"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
+      <c r="N1" s="206"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="138"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="139"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="144"/>
-      <c r="G2" s="145">
-        <v>0</v>
-      </c>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144" t="s">
+      <c r="F2" s="142"/>
+      <c r="G2" s="143">
+        <v>0</v>
+      </c>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="146">
-        <v>2200000</v>
-      </c>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="149"/>
+      <c r="K2" s="144">
+        <v>2400000</v>
+      </c>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="145"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="147"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="141"/>
-      <c r="B3" s="142"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="147"/>
-      <c r="O3" s="148"/>
-      <c r="P3" s="149"/>
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="139"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="146"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="20"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="212" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="214"/>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="217" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="218"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="219"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="215"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="216"/>
-      <c r="N5" s="216"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="217"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="220"/>
+      <c r="B5" s="221"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="221"/>
+      <c r="F5" s="221"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="221"/>
+      <c r="K5" s="221"/>
+      <c r="L5" s="221"/>
+      <c r="M5" s="221"/>
+      <c r="N5" s="221"/>
+      <c r="O5" s="221"/>
+      <c r="P5" s="222"/>
       <c r="Q5" s="20"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="215"/>
-      <c r="B6" s="216"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="216"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="216"/>
-      <c r="N6" s="216"/>
-      <c r="O6" s="216"/>
-      <c r="P6" s="217"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="220"/>
+      <c r="B6" s="221"/>
+      <c r="C6" s="221"/>
+      <c r="D6" s="221"/>
+      <c r="E6" s="221"/>
+      <c r="F6" s="221"/>
+      <c r="G6" s="221"/>
+      <c r="H6" s="221"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="221"/>
+      <c r="O6" s="221"/>
+      <c r="P6" s="222"/>
       <c r="Q6" s="20"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="216"/>
-      <c r="P7" s="217"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="220"/>
+      <c r="B7" s="221"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="221"/>
+      <c r="J7" s="221"/>
+      <c r="K7" s="221"/>
+      <c r="L7" s="221"/>
+      <c r="M7" s="221"/>
+      <c r="N7" s="221"/>
+      <c r="O7" s="221"/>
+      <c r="P7" s="222"/>
       <c r="Q7" s="20"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="218"/>
-      <c r="B8" s="219"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="220"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="223" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="224"/>
-      <c r="C9" s="224"/>
-      <c r="D9" s="224"/>
-      <c r="E9" s="224"/>
-      <c r="F9" s="224"/>
-      <c r="G9" s="224"/>
-      <c r="H9" s="224"/>
-      <c r="I9" s="224"/>
-      <c r="J9" s="224"/>
-      <c r="K9" s="224"/>
-      <c r="L9" s="224"/>
-      <c r="M9" s="224"/>
-      <c r="N9" s="224"/>
-      <c r="O9" s="224"/>
-      <c r="P9" s="224"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="225" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="223"/>
+      <c r="B8" s="224"/>
+      <c r="C8" s="224"/>
+      <c r="D8" s="224"/>
+      <c r="E8" s="224"/>
+      <c r="F8" s="224"/>
+      <c r="G8" s="224"/>
+      <c r="H8" s="224"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="224"/>
+      <c r="K8" s="224"/>
+      <c r="L8" s="224"/>
+      <c r="M8" s="224"/>
+      <c r="N8" s="224"/>
+      <c r="O8" s="224"/>
+      <c r="P8" s="225"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="228" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="229"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="229"/>
+      <c r="P9" s="229"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="230" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="225"/>
-      <c r="I10" s="225"/>
-      <c r="J10" s="225"/>
-      <c r="K10" s="225"/>
-      <c r="L10" s="225"/>
-      <c r="M10" s="225"/>
-      <c r="N10" s="225"/>
-      <c r="O10" s="225"/>
-      <c r="P10" s="225"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="206" t="s">
+      <c r="B10" s="230"/>
+      <c r="C10" s="230"/>
+      <c r="D10" s="230"/>
+      <c r="E10" s="230"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="230"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="230"/>
+      <c r="K10" s="230"/>
+      <c r="L10" s="230"/>
+      <c r="M10" s="230"/>
+      <c r="N10" s="230"/>
+      <c r="O10" s="230"/>
+      <c r="P10" s="230"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="211" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="117"/>
-      <c r="C11" s="206" t="s">
+      <c r="C11" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="206" t="s">
+      <c r="D11" s="211" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="206" t="s">
+      <c r="E11" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="202" t="s">
+      <c r="F11" s="207" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="206" t="s">
+      <c r="G11" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="208" t="s">
+      <c r="H11" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="202" t="s">
+      <c r="I11" s="207" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="202" t="s">
+      <c r="J11" s="207" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="210" t="s">
+      <c r="K11" s="215" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="202" t="s">
+      <c r="L11" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="202" t="s">
-        <v>144</v>
+      <c r="M11" s="207" t="s">
+        <v>130</v>
       </c>
       <c r="N11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="204" t="s">
+      <c r="O11" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="221" t="s">
+      <c r="P11" s="226" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="207"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="212"/>
       <c r="B12" s="118"/>
-      <c r="C12" s="207"/>
-      <c r="D12" s="226"/>
-      <c r="E12" s="207"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="207"/>
-      <c r="H12" s="209"/>
-      <c r="I12" s="203"/>
-      <c r="J12" s="203"/>
-      <c r="K12" s="211"/>
-      <c r="L12" s="203"/>
-      <c r="M12" s="203"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="208"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="214"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="216"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="208"/>
       <c r="N12" s="42" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O12" s="205"/>
-      <c r="P12" s="222"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="210"/>
+      <c r="P12" s="227"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45">
         <v>1</v>
       </c>
@@ -3157,105 +3141,105 @@
         <v>264000.01</v>
       </c>
       <c r="G13" s="56">
-        <f>290400.01-F29-F30</f>
-        <v>263999.66000000003</v>
+        <f>F13</f>
+        <v>264000.01</v>
       </c>
       <c r="H13" s="57">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>0.34999999997671694</v>
+        <v>0</v>
       </c>
       <c r="I13" s="57">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>1.0499999999301507E-2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="107">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
-        <v>264000</v>
+        <v>288000</v>
       </c>
       <c r="K13" s="107">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="168">
+      <c r="L13" s="166">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="M13" s="185"/>
-      <c r="N13" s="167">
+      <c r="M13" s="183"/>
+      <c r="N13" s="165">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>264000.01</v>
+        <v>288000.01</v>
       </c>
       <c r="O13" s="58">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>279840.01</v>
+        <v>305280.01</v>
       </c>
       <c r="P13" s="59">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>271920.01</v>
+        <v>296640.01</v>
       </c>
       <c r="Q13" s="30">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="160">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="158">
         <v>2</v>
       </c>
-      <c r="B14" s="160" t="s">
+      <c r="B14" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="160" t="s">
+      <c r="C14" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="161"/>
-      <c r="E14" s="162">
+      <c r="D14" s="159"/>
+      <c r="E14" s="160">
         <v>6.6</v>
       </c>
       <c r="F14" s="56">
-        <v>176956.02</v>
+        <v>179889.02</v>
       </c>
       <c r="G14" s="56">
-        <v>177000</v>
-      </c>
-      <c r="H14" s="163">
+        <v>180000</v>
+      </c>
+      <c r="H14" s="161">
         <f t="shared" si="0"/>
-        <v>-43.980000000010477</v>
-      </c>
-      <c r="I14" s="163">
+        <v>-110.98000000001048</v>
+      </c>
+      <c r="I14" s="161">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="162">
         <f t="shared" si="1"/>
-        <v>145200</v>
-      </c>
-      <c r="K14" s="164">
+        <v>158400</v>
+      </c>
+      <c r="K14" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="171">
+      <c r="L14" s="169">
         <f>EDESUR!I6</f>
-        <v>34733.22</v>
-      </c>
-      <c r="M14" s="186"/>
-      <c r="N14" s="167">
+        <v>31125.624497318255</v>
+      </c>
+      <c r="M14" s="184"/>
+      <c r="N14" s="165">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>179889.02</v>
-      </c>
-      <c r="O14" s="165">
+        <v>189415.02</v>
+      </c>
+      <c r="O14" s="163">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>190682.02</v>
-      </c>
-      <c r="P14" s="166">
+        <v>200780.02</v>
+      </c>
+      <c r="P14" s="164">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>185286.02</v>
+        <v>195097.02</v>
       </c>
       <c r="Q14" s="30">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45">
         <v>3</v>
       </c>
@@ -3272,11 +3256,11 @@
         <v>5.4</v>
       </c>
       <c r="F15" s="55">
-        <v>156679.03</v>
+        <v>188075.03</v>
       </c>
       <c r="G15" s="56">
         <f>F15</f>
-        <v>156679.03</v>
+        <v>188075.03</v>
       </c>
       <c r="H15" s="57">
         <f t="shared" si="0"/>
@@ -3288,37 +3272,35 @@
       </c>
       <c r="J15" s="107">
         <f t="shared" si="1"/>
-        <v>118800</v>
+        <v>129600</v>
       </c>
       <c r="K15" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="168">
+      <c r="L15" s="166">
         <f>EDESUR!I7</f>
-        <v>19275.349999999999</v>
-      </c>
-      <c r="M15" s="184">
-        <v>50000</v>
-      </c>
-      <c r="N15" s="167">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="M15" s="182"/>
+      <c r="N15" s="165">
         <f t="shared" si="4"/>
-        <v>188075.03</v>
+        <v>135021.03</v>
       </c>
       <c r="O15" s="58">
         <f t="shared" si="5"/>
-        <v>199360.03</v>
+        <v>143122.03</v>
       </c>
       <c r="P15" s="59">
         <f t="shared" si="6"/>
-        <v>193717.03</v>
+        <v>139072.03</v>
       </c>
       <c r="Q15" s="30">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45">
         <v>4</v>
       </c>
@@ -3329,7 +3311,7 @@
         <v>34</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E16" s="54">
         <v>6.6</v>
@@ -3338,102 +3320,104 @@
         <v>145200.04</v>
       </c>
       <c r="G16" s="56">
-        <f>F16</f>
-        <v>145200.04</v>
+        <f>158400.2-G32</f>
+        <v>145200</v>
       </c>
       <c r="H16" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.0000000008149073E-2</v>
       </c>
       <c r="I16" s="57">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2000000002444721E-3</v>
       </c>
       <c r="J16" s="107">
         <f t="shared" si="1"/>
-        <v>145200</v>
+        <v>158400</v>
       </c>
       <c r="K16" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="168">
+      <c r="L16" s="166">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="M16" s="185"/>
-      <c r="N16" s="167">
+      <c r="M16" s="183"/>
+      <c r="N16" s="165">
         <f t="shared" si="4"/>
-        <v>145200.04</v>
+        <v>158400.04</v>
       </c>
       <c r="O16" s="58">
         <f t="shared" si="5"/>
-        <v>153912.04</v>
+        <v>167904.04</v>
       </c>
       <c r="P16" s="59">
         <f t="shared" si="6"/>
-        <v>149556.04</v>
+        <v>163152.04</v>
       </c>
       <c r="Q16" s="30">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="160">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="158">
         <v>5</v>
       </c>
-      <c r="B17" s="160" t="s">
+      <c r="B17" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="160" t="s">
+      <c r="C17" s="158" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="160" t="s">
+      <c r="D17" s="158" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="162">
+      <c r="E17" s="160">
         <v>6.6</v>
       </c>
       <c r="F17" s="56">
-        <v>144400.04999999999</v>
+        <v>145200.04999999999</v>
       </c>
       <c r="G17" s="56">
         <f>F17</f>
-        <v>144400.04999999999</v>
-      </c>
-      <c r="H17" s="163">
+        <v>145200.04999999999</v>
+      </c>
+      <c r="H17" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="163">
+      <c r="I17" s="161">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="164">
+      <c r="J17" s="162">
         <f t="shared" si="1"/>
-        <v>145200</v>
-      </c>
-      <c r="K17" s="164">
+        <v>158400</v>
+      </c>
+      <c r="K17" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="171">
+      <c r="L17" s="169">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="M17" s="186"/>
-      <c r="N17" s="167">
+      <c r="M17" s="184">
+        <v>50000</v>
+      </c>
+      <c r="N17" s="165">
         <f t="shared" si="4"/>
-        <v>145200.04999999999</v>
-      </c>
-      <c r="O17" s="165">
+        <v>208400.05</v>
+      </c>
+      <c r="O17" s="163">
         <f t="shared" si="5"/>
-        <v>153912.04999999999</v>
-      </c>
-      <c r="P17" s="166">
+        <v>220904.05</v>
+      </c>
+      <c r="P17" s="164">
         <f t="shared" si="6"/>
-        <v>149556.04999999999</v>
+        <v>214652.05</v>
       </c>
       <c r="Q17" s="30">
         <f t="shared" si="7"/>
@@ -3443,7 +3427,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45">
         <v>6</v>
       </c>
@@ -3476,157 +3460,157 @@
       </c>
       <c r="J18" s="107">
         <f t="shared" si="1"/>
-        <v>118800</v>
+        <v>129600</v>
       </c>
       <c r="K18" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="168">
+      <c r="L18" s="166">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="M18" s="185"/>
-      <c r="N18" s="167">
+      <c r="M18" s="183"/>
+      <c r="N18" s="165">
         <f t="shared" si="4"/>
-        <v>118800.06</v>
+        <v>129600.06</v>
       </c>
       <c r="O18" s="58">
         <f t="shared" si="5"/>
-        <v>125928.06</v>
+        <v>137376.06</v>
       </c>
       <c r="P18" s="59">
         <f t="shared" si="6"/>
-        <v>122364.06</v>
+        <v>133488.06</v>
       </c>
       <c r="Q18" s="30">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="160">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="158">
         <v>7</v>
       </c>
-      <c r="B19" s="160" t="s">
+      <c r="B19" s="158" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="160" t="s">
+      <c r="C19" s="158" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="160" t="s">
+      <c r="D19" s="158" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="162">
+      <c r="E19" s="160">
         <v>5.4</v>
       </c>
       <c r="F19" s="56">
-        <v>267756.07</v>
+        <v>122364.07</v>
       </c>
       <c r="G19" s="56">
         <f>F19</f>
-        <v>267756.07</v>
-      </c>
-      <c r="H19" s="163">
+        <v>122364.07</v>
+      </c>
+      <c r="H19" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="163">
+      <c r="I19" s="161">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="164">
+      <c r="J19" s="162">
         <f t="shared" si="1"/>
-        <v>118800</v>
-      </c>
-      <c r="K19" s="164">
+        <v>129600</v>
+      </c>
+      <c r="K19" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="168">
+      <c r="L19" s="166">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M19" s="185"/>
-      <c r="N19" s="167">
+      <c r="M19" s="183"/>
+      <c r="N19" s="165">
         <f t="shared" si="4"/>
-        <v>118800.07</v>
-      </c>
-      <c r="O19" s="165">
+        <v>129600.07</v>
+      </c>
+      <c r="O19" s="163">
         <f t="shared" si="5"/>
-        <v>125928.07</v>
-      </c>
-      <c r="P19" s="166">
+        <v>137376.07</v>
+      </c>
+      <c r="P19" s="164">
         <f t="shared" si="6"/>
-        <v>122364.07</v>
+        <v>133488.07</v>
       </c>
       <c r="Q19" s="30">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="160">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="158">
         <v>8</v>
       </c>
-      <c r="B20" s="160" t="s">
+      <c r="B20" s="158" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="160" t="s">
+      <c r="C20" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="161" t="s">
+      <c r="D20" s="159" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="162">
+      <c r="E20" s="160">
         <v>6.6</v>
       </c>
       <c r="F20" s="56">
-        <v>245886.07999999999</v>
+        <v>222130.08</v>
       </c>
       <c r="G20" s="56">
         <f>F20</f>
-        <v>245886.07999999999</v>
-      </c>
-      <c r="H20" s="163">
+        <v>222130.08</v>
+      </c>
+      <c r="H20" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="163">
+      <c r="I20" s="161">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="164">
+      <c r="J20" s="162">
         <f t="shared" si="1"/>
-        <v>145200</v>
-      </c>
-      <c r="K20" s="164">
+        <v>158400</v>
+      </c>
+      <c r="K20" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="168">
+      <c r="L20" s="166">
         <f>EDESUR!I13</f>
-        <v>70460.03</v>
-      </c>
-      <c r="M20" s="185"/>
-      <c r="N20" s="167">
+        <v>66680.352219450724</v>
+      </c>
+      <c r="M20" s="183"/>
+      <c r="N20" s="165">
         <f t="shared" si="4"/>
-        <v>215660.08</v>
-      </c>
-      <c r="O20" s="165">
+        <v>225080.08</v>
+      </c>
+      <c r="O20" s="163">
         <f t="shared" si="5"/>
-        <v>228600.08</v>
-      </c>
-      <c r="P20" s="166">
+        <v>238585.08</v>
+      </c>
+      <c r="P20" s="164">
         <f t="shared" si="6"/>
-        <v>222130.08</v>
+        <v>231832.08</v>
       </c>
       <c r="Q20" s="30">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45">
         <v>9</v>
       </c>
@@ -3646,12 +3630,12 @@
         <v>106012.09</v>
       </c>
       <c r="G21" s="56">
-        <f>F21+39187.9</f>
-        <v>145199.99</v>
+        <f>F21</f>
+        <v>106012.09</v>
       </c>
       <c r="H21" s="57">
         <f t="shared" si="0"/>
-        <v>-39187.899999999994</v>
+        <v>0</v>
       </c>
       <c r="I21" s="57">
         <f t="shared" si="3"/>
@@ -3659,35 +3643,35 @@
       </c>
       <c r="J21" s="107">
         <f t="shared" si="1"/>
-        <v>145200</v>
+        <v>158400</v>
       </c>
       <c r="K21" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="168">
+      <c r="L21" s="166">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="185"/>
-      <c r="N21" s="167">
+      <c r="M21" s="183"/>
+      <c r="N21" s="165">
         <f t="shared" si="4"/>
-        <v>106012.09</v>
+        <v>158400.09</v>
       </c>
       <c r="O21" s="58">
         <f t="shared" si="5"/>
-        <v>112373.09</v>
+        <v>167904.09</v>
       </c>
       <c r="P21" s="59">
         <f t="shared" si="6"/>
-        <v>109192.09</v>
+        <v>163152.09</v>
       </c>
       <c r="Q21" s="30">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45">
         <v>10</v>
       </c>
@@ -3707,12 +3691,12 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="G22" s="56">
-        <f>RESUMEN!D43-39187.9</f>
-        <v>118800.39000000001</v>
+        <f>RESUMEN!D42</f>
+        <v>157988.29</v>
       </c>
       <c r="H22" s="57">
         <f>F22-G22</f>
-        <v>-118800.29000000001</v>
+        <v>-157988.19</v>
       </c>
       <c r="I22" s="57">
         <f t="shared" si="3"/>
@@ -3720,35 +3704,35 @@
       </c>
       <c r="J22" s="107">
         <f t="shared" si="1"/>
-        <v>118800</v>
+        <v>129600</v>
       </c>
       <c r="K22" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="168">
+      <c r="L22" s="166">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="M22" s="185"/>
-      <c r="N22" s="167">
+      <c r="M22" s="183"/>
+      <c r="N22" s="165">
         <f t="shared" si="4"/>
-        <v>9.9999999999999992E-2</v>
+        <v>-28387.9</v>
       </c>
       <c r="O22" s="58">
         <f t="shared" si="5"/>
-        <v>9.9999999999999992E-2</v>
+        <v>-30090.9</v>
       </c>
       <c r="P22" s="59">
         <f t="shared" si="6"/>
-        <v>9.9999999999999992E-2</v>
+        <v>-29239.9</v>
       </c>
       <c r="Q22" s="30">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45">
         <v>11</v>
       </c>
@@ -3779,28 +3763,28 @@
       </c>
       <c r="J23" s="107">
         <f t="shared" si="1"/>
-        <v>118800</v>
+        <v>129600</v>
       </c>
       <c r="K23" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="168">
+      <c r="L23" s="166">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M23" s="185"/>
-      <c r="N23" s="167">
+      <c r="M23" s="183"/>
+      <c r="N23" s="165">
         <f t="shared" si="4"/>
-        <v>118800.11</v>
+        <v>129600.11</v>
       </c>
       <c r="O23" s="58">
         <f t="shared" si="5"/>
-        <v>125928.11</v>
+        <v>137376.10999999999</v>
       </c>
       <c r="P23" s="59">
         <f t="shared" si="6"/>
-        <v>122364.11</v>
+        <v>133488.10999999999</v>
       </c>
       <c r="Q23" s="30">
         <f t="shared" si="7"/>
@@ -3810,7 +3794,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45">
         <v>12</v>
       </c>
@@ -3827,11 +3811,11 @@
         <v>6.6</v>
       </c>
       <c r="F24" s="55">
-        <v>158784.12</v>
+        <v>145200.12</v>
       </c>
       <c r="G24" s="56">
         <f>F24</f>
-        <v>158784.12</v>
+        <v>145200.12</v>
       </c>
       <c r="H24" s="57">
         <f t="shared" si="0"/>
@@ -3843,35 +3827,35 @@
       </c>
       <c r="J24" s="107">
         <f t="shared" si="1"/>
-        <v>145200</v>
+        <v>158400</v>
       </c>
       <c r="K24" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="168">
+      <c r="L24" s="166">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="M24" s="185"/>
-      <c r="N24" s="167">
+      <c r="M24" s="183"/>
+      <c r="N24" s="165">
         <f t="shared" si="4"/>
-        <v>145200.12</v>
+        <v>158400.12</v>
       </c>
       <c r="O24" s="58">
         <f t="shared" si="5"/>
-        <v>153912.12</v>
+        <v>167904.12</v>
       </c>
       <c r="P24" s="59">
         <f t="shared" si="6"/>
-        <v>149556.12</v>
+        <v>163152.12</v>
       </c>
       <c r="Q24" s="30">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45">
         <v>13</v>
       </c>
@@ -3888,15 +3872,14 @@
         <v>6.6</v>
       </c>
       <c r="F25" s="55">
-        <v>140959.13</v>
+        <v>145200.13</v>
       </c>
       <c r="G25" s="56">
-        <f>F25</f>
-        <v>140959.13</v>
+        <v>149556.13</v>
       </c>
       <c r="H25" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4356</v>
       </c>
       <c r="I25" s="57">
         <f t="shared" si="3"/>
@@ -3904,46 +3887,46 @@
       </c>
       <c r="J25" s="107">
         <f t="shared" si="1"/>
-        <v>145200</v>
+        <v>158400</v>
       </c>
       <c r="K25" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="168">
+      <c r="L25" s="166">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="M25" s="185"/>
-      <c r="N25" s="167">
+      <c r="M25" s="183"/>
+      <c r="N25" s="165">
         <f t="shared" si="4"/>
-        <v>145200.13</v>
+        <v>154044.13</v>
       </c>
       <c r="O25" s="58">
         <f t="shared" si="5"/>
-        <v>153912.13</v>
+        <v>163287.13</v>
       </c>
       <c r="P25" s="59">
         <f t="shared" si="6"/>
-        <v>149556.13</v>
+        <v>158665.13</v>
       </c>
       <c r="Q25" s="30">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="160">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="158">
         <v>14</v>
       </c>
-      <c r="B26" s="160" t="s">
+      <c r="B26" s="158" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="160" t="s">
+      <c r="C26" s="158" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="161"/>
-      <c r="E26" s="162">
+      <c r="D26" s="159"/>
+      <c r="E26" s="160">
         <v>5.4</v>
       </c>
       <c r="F26" s="56">
@@ -3953,45 +3936,45 @@
         <f>F26</f>
         <v>118800.14</v>
       </c>
-      <c r="H26" s="163">
+      <c r="H26" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="163">
+      <c r="I26" s="161">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="164">
+      <c r="J26" s="162">
         <f t="shared" si="1"/>
-        <v>118800</v>
-      </c>
-      <c r="K26" s="164">
+        <v>129600</v>
+      </c>
+      <c r="K26" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="171">
+      <c r="L26" s="169">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="M26" s="186"/>
-      <c r="N26" s="167">
+      <c r="M26" s="184"/>
+      <c r="N26" s="165">
         <f t="shared" si="4"/>
-        <v>118800.14</v>
-      </c>
-      <c r="O26" s="165">
+        <v>129600.14</v>
+      </c>
+      <c r="O26" s="163">
         <f t="shared" si="5"/>
-        <v>125928.14</v>
-      </c>
-      <c r="P26" s="166">
+        <v>137376.14000000001</v>
+      </c>
+      <c r="P26" s="164">
         <f t="shared" si="6"/>
-        <v>122364.14</v>
+        <v>133488.14000000001</v>
       </c>
       <c r="Q26" s="30">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45">
         <v>15</v>
       </c>
@@ -4006,50 +3989,51 @@
         <v>5.4</v>
       </c>
       <c r="F27" s="55">
-        <v>118800.15</v>
+        <v>241164.15</v>
       </c>
       <c r="G27" s="56">
-        <v>0</v>
+        <f>F27</f>
+        <v>241164.15</v>
       </c>
       <c r="H27" s="57">
         <f t="shared" si="0"/>
-        <v>118800.15</v>
+        <v>0</v>
       </c>
       <c r="I27" s="57">
         <f t="shared" si="3"/>
-        <v>3564.0044999999996</v>
+        <v>0</v>
       </c>
       <c r="J27" s="107">
         <f t="shared" si="1"/>
-        <v>118800</v>
+        <v>129600</v>
       </c>
       <c r="K27" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="168">
+      <c r="L27" s="166">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="M27" s="185"/>
-      <c r="N27" s="167">
+      <c r="M27" s="183"/>
+      <c r="N27" s="165">
         <f t="shared" si="4"/>
-        <v>241164.15</v>
+        <v>129600.15</v>
       </c>
       <c r="O27" s="58">
         <f t="shared" si="5"/>
-        <v>255634.15</v>
+        <v>137376.15</v>
       </c>
       <c r="P27" s="59">
         <f t="shared" si="6"/>
-        <v>248399.15</v>
+        <v>133488.15</v>
       </c>
       <c r="Q27" s="30">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45">
         <v>16</v>
       </c>
@@ -4082,35 +4066,35 @@
       </c>
       <c r="J28" s="107">
         <f t="shared" si="1"/>
-        <v>15400</v>
+        <v>16800</v>
       </c>
       <c r="K28" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="168">
+      <c r="L28" s="166">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="M28" s="185"/>
-      <c r="N28" s="167">
+      <c r="M28" s="183"/>
+      <c r="N28" s="165">
         <f t="shared" si="4"/>
-        <v>15400.16</v>
+        <v>16800.16</v>
       </c>
       <c r="O28" s="58">
         <f t="shared" si="5"/>
-        <v>16324.16</v>
+        <v>17808.16</v>
       </c>
       <c r="P28" s="59">
         <f t="shared" si="6"/>
-        <v>15862.16</v>
+        <v>17304.16</v>
       </c>
       <c r="Q28" s="30">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="45">
         <v>17</v>
       </c>
@@ -4128,12 +4112,11 @@
         <v>13200.17</v>
       </c>
       <c r="G29" s="56">
-        <f t="shared" si="9"/>
-        <v>13200.17</v>
+        <v>26400.17</v>
       </c>
       <c r="H29" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-13199.999999999998</v>
       </c>
       <c r="I29" s="57">
         <f t="shared" si="3"/>
@@ -4141,35 +4124,35 @@
       </c>
       <c r="J29" s="107">
         <f t="shared" si="1"/>
-        <v>13200</v>
+        <v>14400</v>
       </c>
       <c r="K29" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="168">
+      <c r="L29" s="166">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="M29" s="185"/>
-      <c r="N29" s="167">
+      <c r="M29" s="183"/>
+      <c r="N29" s="165">
         <f t="shared" si="4"/>
-        <v>13200.17</v>
+        <v>1200.17</v>
       </c>
       <c r="O29" s="58">
         <f t="shared" si="5"/>
-        <v>13992.17</v>
+        <v>1272.17</v>
       </c>
       <c r="P29" s="59">
         <f t="shared" si="6"/>
-        <v>13596.17</v>
+        <v>1236.17</v>
       </c>
       <c r="Q29" s="30">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="45">
         <v>18</v>
       </c>
@@ -4187,104 +4170,103 @@
         <v>13200.18</v>
       </c>
       <c r="G30" s="56">
-        <f t="shared" si="9"/>
-        <v>13200.18</v>
+        <v>0</v>
       </c>
       <c r="H30" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13200.18</v>
       </c>
       <c r="I30" s="57">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>396.00540000000001</v>
       </c>
       <c r="J30" s="107">
         <f t="shared" si="1"/>
-        <v>13200</v>
+        <v>14400</v>
       </c>
       <c r="K30" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="168">
+      <c r="L30" s="166">
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="M30" s="185"/>
-      <c r="N30" s="167">
+      <c r="M30" s="183"/>
+      <c r="N30" s="165">
         <f t="shared" si="4"/>
-        <v>13200.18</v>
+        <v>27996.18</v>
       </c>
       <c r="O30" s="58">
         <f t="shared" si="5"/>
-        <v>13992.18</v>
+        <v>29676.18</v>
       </c>
       <c r="P30" s="59">
         <f t="shared" si="6"/>
-        <v>13596.18</v>
+        <v>28836.18</v>
       </c>
       <c r="Q30" s="30">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="160">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="158">
         <v>19</v>
       </c>
-      <c r="B31" s="160" t="s">
+      <c r="B31" s="158" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="160" t="s">
+      <c r="C31" s="158" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="161"/>
-      <c r="E31" s="162">
+      <c r="D31" s="159"/>
+      <c r="E31" s="160">
         <v>0.6</v>
       </c>
       <c r="F31" s="56">
         <v>13200.19</v>
       </c>
       <c r="G31" s="56">
-        <f t="shared" si="9"/>
+        <f>F31</f>
         <v>13200.19</v>
       </c>
-      <c r="H31" s="163">
+      <c r="H31" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="163">
+      <c r="I31" s="161">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="164">
+      <c r="J31" s="162">
         <f t="shared" si="1"/>
-        <v>13200</v>
-      </c>
-      <c r="K31" s="164">
+        <v>14400</v>
+      </c>
+      <c r="K31" s="162">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="171">
+      <c r="L31" s="169">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="M31" s="186"/>
-      <c r="N31" s="167">
+      <c r="M31" s="184"/>
+      <c r="N31" s="165">
         <f t="shared" si="4"/>
-        <v>13200.19</v>
-      </c>
-      <c r="O31" s="165"/>
-      <c r="P31" s="166">
+        <v>14400.19</v>
+      </c>
+      <c r="O31" s="163"/>
+      <c r="P31" s="164">
         <f t="shared" si="6"/>
-        <v>13596.19</v>
+        <v>14832.19</v>
       </c>
       <c r="Q31" s="30">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>20</v>
       </c>
@@ -4295,7 +4277,7 @@
         <v>34</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32" s="54">
         <v>0.6</v>
@@ -4317,32 +4299,32 @@
       </c>
       <c r="J32" s="107">
         <f t="shared" si="1"/>
-        <v>13200</v>
+        <v>14400</v>
       </c>
       <c r="K32" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="168">
+      <c r="L32" s="166">
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="M32" s="185"/>
-      <c r="N32" s="167">
+      <c r="M32" s="183"/>
+      <c r="N32" s="165">
         <f t="shared" si="4"/>
-        <v>13200.2</v>
+        <v>14400.2</v>
       </c>
       <c r="O32" s="58"/>
       <c r="P32" s="59">
         <f t="shared" si="6"/>
-        <v>13596.2</v>
+        <v>14832.2</v>
       </c>
       <c r="Q32" s="30">
         <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>21</v>
       </c>
@@ -4362,45 +4344,44 @@
         <v>6600.21</v>
       </c>
       <c r="G33" s="56">
-        <f t="shared" si="9"/>
-        <v>6600.21</v>
+        <v>0</v>
       </c>
       <c r="H33" s="57">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6600.21</v>
       </c>
       <c r="I33" s="57">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>198.00629999999998</v>
       </c>
       <c r="J33" s="107">
         <f t="shared" si="1"/>
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="K33" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="168">
+      <c r="L33" s="166">
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="M33" s="185"/>
-      <c r="N33" s="167">
+      <c r="M33" s="183"/>
+      <c r="N33" s="165">
         <f t="shared" si="4"/>
-        <v>6600.21</v>
+        <v>13998.21</v>
       </c>
       <c r="O33" s="58"/>
       <c r="P33" s="59">
         <f t="shared" si="6"/>
-        <v>6798.21</v>
+        <v>14418.21</v>
       </c>
       <c r="Q33" s="30">
         <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="61">
         <v>22</v>
       </c>
@@ -4417,7 +4398,7 @@
       <c r="F34" s="62">
         <v>6600.22</v>
       </c>
-      <c r="G34" s="159">
+      <c r="G34" s="157">
         <f t="shared" si="9"/>
         <v>6600.22</v>
       </c>
@@ -4431,32 +4412,32 @@
       </c>
       <c r="J34" s="107">
         <f t="shared" si="1"/>
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="K34" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="168">
+      <c r="L34" s="166">
         <f>EDESUR!I28</f>
         <v>0</v>
       </c>
-      <c r="M34" s="185"/>
-      <c r="N34" s="167">
+      <c r="M34" s="183"/>
+      <c r="N34" s="165">
         <f t="shared" si="4"/>
-        <v>6600.22</v>
+        <v>7200.22</v>
       </c>
       <c r="O34" s="58"/>
       <c r="P34" s="59">
         <f t="shared" si="6"/>
-        <v>6798.22</v>
+        <v>7416.22</v>
       </c>
       <c r="Q34" s="30">
         <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45">
         <v>23</v>
       </c>
@@ -4489,32 +4470,32 @@
       </c>
       <c r="J35" s="107">
         <f t="shared" si="1"/>
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="K35" s="107">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="168">
+      <c r="L35" s="166">
         <f>EDESUR!I29</f>
         <v>0</v>
       </c>
-      <c r="M35" s="185"/>
-      <c r="N35" s="167">
+      <c r="M35" s="183"/>
+      <c r="N35" s="165">
         <f t="shared" si="4"/>
-        <v>6600.23</v>
+        <v>7200.23</v>
       </c>
       <c r="O35" s="64"/>
       <c r="P35" s="59">
         <f t="shared" si="6"/>
-        <v>6798.23</v>
+        <v>7416.23</v>
       </c>
       <c r="Q35" s="30">
         <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="65"/>
       <c r="B36" s="65"/>
       <c r="C36" s="66"/>
@@ -4525,23 +4506,23 @@
       </c>
       <c r="F36" s="39">
         <f>SUM(F13:F35)</f>
-        <v>2369834.7600000012</v>
+        <v>2348836.7600000012</v>
       </c>
       <c r="G36" s="43">
         <f>SUM(G13:G35)</f>
-        <v>2409066.1000000006</v>
+        <v>2504691.1700000009</v>
       </c>
       <c r="H36" s="43">
         <f>SUM(H13:H35)</f>
-        <v>-39231.340000000055</v>
+        <v>-155854.41</v>
       </c>
       <c r="I36" s="43">
         <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
-        <v>3564.024899999999</v>
+        <v>594.0228000000003</v>
       </c>
       <c r="J36" s="93">
         <f t="shared" si="11"/>
-        <v>2200000</v>
+        <v>2400000</v>
       </c>
       <c r="K36" s="43">
         <f t="shared" si="11"/>
@@ -4549,113 +4530,113 @@
       </c>
       <c r="L36" s="67">
         <f>SUM(L13:L35)</f>
-        <v>124468.6</v>
+        <v>103227.02696710824</v>
       </c>
       <c r="M36" s="67"/>
       <c r="N36" s="67">
         <f>SUM(N13:N35)</f>
-        <v>2338802.7600000012</v>
+        <v>2397968.7600000012</v>
       </c>
       <c r="O36" s="67">
         <f t="shared" si="11"/>
-        <v>2430158.7100000009</v>
+        <v>2481216.7100000009</v>
       </c>
       <c r="P36" s="67">
         <f>SUM(P13:P35)</f>
-        <v>2408966.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2469906.7600000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="36"/>
       <c r="D37" s="36"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="198" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="203" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="198"/>
-      <c r="E39" s="198"/>
-      <c r="F39" s="198"/>
-      <c r="G39" s="198"/>
-      <c r="H39" s="198"/>
-      <c r="I39" s="198"/>
-      <c r="J39" s="198"/>
-      <c r="K39" s="198"/>
-      <c r="L39" s="198"/>
-      <c r="M39" s="198"/>
-      <c r="N39" s="198"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="198"/>
-      <c r="D40" s="198"/>
-      <c r="E40" s="198"/>
-      <c r="F40" s="198"/>
-      <c r="G40" s="198"/>
-      <c r="H40" s="198"/>
-      <c r="I40" s="198"/>
-      <c r="J40" s="198"/>
-      <c r="K40" s="198"/>
-      <c r="L40" s="198"/>
-      <c r="M40" s="198"/>
-      <c r="N40" s="198"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="198"/>
-      <c r="D41" s="198"/>
-      <c r="E41" s="198"/>
-      <c r="F41" s="198"/>
-      <c r="G41" s="198"/>
-      <c r="H41" s="198"/>
-      <c r="I41" s="198"/>
-      <c r="J41" s="198"/>
-      <c r="K41" s="198"/>
-      <c r="L41" s="198"/>
-      <c r="M41" s="198"/>
-      <c r="N41" s="198"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="198"/>
-      <c r="D42" s="198"/>
-      <c r="E42" s="198"/>
-      <c r="F42" s="198"/>
-      <c r="G42" s="198"/>
-      <c r="H42" s="198"/>
-      <c r="I42" s="198"/>
-      <c r="J42" s="198"/>
-      <c r="K42" s="198"/>
-      <c r="L42" s="198"/>
-      <c r="M42" s="198"/>
-      <c r="N42" s="198"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="198"/>
-      <c r="D43" s="198"/>
-      <c r="E43" s="198"/>
-      <c r="F43" s="198"/>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="198"/>
-      <c r="D44" s="198"/>
-      <c r="E44" s="198"/>
-      <c r="F44" s="198"/>
-      <c r="G44" s="198"/>
-      <c r="H44" s="198"/>
-      <c r="I44" s="198"/>
-      <c r="J44" s="198"/>
-      <c r="K44" s="198"/>
-      <c r="L44" s="198"/>
-      <c r="M44" s="198"/>
-      <c r="N44" s="198"/>
+      <c r="D39" s="203"/>
+      <c r="E39" s="203"/>
+      <c r="F39" s="203"/>
+      <c r="G39" s="203"/>
+      <c r="H39" s="203"/>
+      <c r="I39" s="203"/>
+      <c r="J39" s="203"/>
+      <c r="K39" s="203"/>
+      <c r="L39" s="203"/>
+      <c r="M39" s="203"/>
+      <c r="N39" s="203"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="203"/>
+      <c r="I40" s="203"/>
+      <c r="J40" s="203"/>
+      <c r="K40" s="203"/>
+      <c r="L40" s="203"/>
+      <c r="M40" s="203"/>
+      <c r="N40" s="203"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+      <c r="G41" s="203"/>
+      <c r="H41" s="203"/>
+      <c r="I41" s="203"/>
+      <c r="J41" s="203"/>
+      <c r="K41" s="203"/>
+      <c r="L41" s="203"/>
+      <c r="M41" s="203"/>
+      <c r="N41" s="203"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="203"/>
+      <c r="D42" s="203"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="203"/>
+      <c r="I42" s="203"/>
+      <c r="J42" s="203"/>
+      <c r="K42" s="203"/>
+      <c r="L42" s="203"/>
+      <c r="M42" s="203"/>
+      <c r="N42" s="203"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="203"/>
+      <c r="I43" s="203"/>
+      <c r="J43" s="203"/>
+      <c r="K43" s="203"/>
+      <c r="L43" s="203"/>
+      <c r="M43" s="203"/>
+      <c r="N43" s="203"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="203"/>
+      <c r="D44" s="203"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="203"/>
+      <c r="G44" s="203"/>
+      <c r="H44" s="203"/>
+      <c r="I44" s="203"/>
+      <c r="J44" s="203"/>
+      <c r="K44" s="203"/>
+      <c r="L44" s="203"/>
+      <c r="M44" s="203"/>
+      <c r="N44" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4687,17 +4668,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="125" t="s">
         <v>80</v>
       </c>
@@ -4707,569 +4688,561 @@
       <c r="E3" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="158" t="s">
-        <v>141</v>
-      </c>
-      <c r="I3" s="229" t="s">
+      <c r="G3" s="156" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="234" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="230"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="235"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="125"/>
       <c r="C4" s="125"/>
       <c r="E4" s="125"/>
       <c r="G4" s="128"/>
-      <c r="I4" s="229"/>
-      <c r="J4" s="230"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I4" s="234"/>
+      <c r="J4" s="235"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="125">
         <v>1</v>
       </c>
       <c r="C5" s="125" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="129">
-        <v>11844.04</v>
+      <c r="E5" s="192">
+        <v>12046.778334087237</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="130">
-        <f>E5</f>
-        <v>11844.04</v>
-      </c>
-      <c r="I5" s="227">
+      <c r="G5" s="193">
+        <v>12046.778334087237</v>
+      </c>
+      <c r="I5" s="232">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="228"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="233"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="125">
         <v>1</v>
       </c>
       <c r="C6" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="129">
-        <v>34733.22</v>
+      <c r="E6" s="192">
+        <v>31125.624497318255</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="130">
-        <v>0</v>
-      </c>
-      <c r="I6" s="227">
+      <c r="G6" s="193">
+        <v>0</v>
+      </c>
+      <c r="I6" s="232">
         <f t="shared" ref="I6:I19" si="0">E6-G6</f>
-        <v>34733.22</v>
-      </c>
-      <c r="J6" s="228"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+        <v>31125.624497318255</v>
+      </c>
+      <c r="J6" s="233"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="125">
         <v>1</v>
       </c>
       <c r="C7" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="129">
-        <v>19275.349999999999</v>
+      <c r="E7" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="130"/>
-      <c r="I7" s="227">
+      <c r="G7" s="193">
+        <v>0</v>
+      </c>
+      <c r="I7" s="232">
         <f t="shared" si="0"/>
-        <v>19275.349999999999</v>
-      </c>
-      <c r="J7" s="228"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="J7" s="233"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="125">
         <v>2</v>
       </c>
       <c r="C8" s="125" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="129">
-        <v>5329.82</v>
+      <c r="E8" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="130">
-        <f>E8</f>
-        <v>5329.82</v>
-      </c>
-      <c r="I8" s="227">
+      <c r="G8" s="193">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="I8" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="228"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="233"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="126">
         <v>2</v>
       </c>
       <c r="C9" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="129">
-        <v>6514.22</v>
+      <c r="E9" s="192">
+        <v>6625.7280837479811</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="130">
-        <f>E9</f>
-        <v>6514.22</v>
-      </c>
-      <c r="I9" s="227">
+      <c r="G9" s="193">
+        <v>6625.7280837479811</v>
+      </c>
+      <c r="I9" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="228"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="233"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="126">
         <v>2</v>
       </c>
       <c r="C10" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="129">
-        <v>6514.22</v>
+      <c r="E10" s="192">
+        <v>6625.7280837479811</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="130">
-        <f>E10</f>
-        <v>6514.22</v>
-      </c>
-      <c r="I10" s="227">
+      <c r="G10" s="193">
+        <v>6625.7280837479811</v>
+      </c>
+      <c r="I10" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="228"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="233"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="126">
         <v>2</v>
       </c>
       <c r="C11" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="129">
-        <v>5329.82</v>
+      <c r="E11" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="130">
-        <f>E11</f>
-        <v>5329.82</v>
-      </c>
-      <c r="I11" s="227">
+      <c r="G11" s="193">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="I11" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="228"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="233"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="126">
         <v>3</v>
       </c>
       <c r="C12" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="129">
-        <v>5329.82</v>
+      <c r="E12" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="130">
-        <f>E12</f>
-        <v>5329.82</v>
-      </c>
-      <c r="I12" s="227">
+      <c r="G12" s="193">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="I12" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="228"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="233"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="125">
         <v>3</v>
       </c>
       <c r="C13" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="129">
-        <v>70460.03</v>
+      <c r="E13" s="192">
+        <v>66680.352219450724</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="130"/>
-      <c r="I13" s="227">
+      <c r="G13" s="193">
+        <v>0</v>
+      </c>
+      <c r="I13" s="232">
         <f t="shared" si="0"/>
-        <v>70460.03</v>
-      </c>
-      <c r="J13" s="228"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+        <v>66680.352219450724</v>
+      </c>
+      <c r="J13" s="233"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="126">
         <v>3</v>
       </c>
       <c r="C14" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="129">
-        <v>6514.22</v>
+      <c r="E14" s="192">
+        <v>6625.7280837479811</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="130">
-        <f t="shared" ref="G14:G19" si="1">E14</f>
-        <v>6514.22</v>
-      </c>
-      <c r="I14" s="227">
+      <c r="G14" s="193">
+        <v>6625.7280837479811</v>
+      </c>
+      <c r="I14" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="228"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="233"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="126">
         <v>3</v>
       </c>
       <c r="C15" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="129">
-        <v>5329.82</v>
+      <c r="E15" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="130">
-        <f t="shared" si="1"/>
-        <v>5329.82</v>
-      </c>
-      <c r="I15" s="227">
+      <c r="G15" s="193">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="I15" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="228"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J15" s="233"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="125">
         <v>4</v>
       </c>
       <c r="C16" s="125" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="129">
-        <v>5329.82</v>
+      <c r="E16" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="130">
-        <f t="shared" si="1"/>
-        <v>5329.82</v>
-      </c>
-      <c r="I16" s="227">
+      <c r="G16" s="193">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="I16" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="228"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J16" s="233"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="126">
         <v>4</v>
       </c>
       <c r="C17" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="129">
-        <v>6514.22</v>
+      <c r="E17" s="192">
+        <v>6625.7280837479811</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="130">
-        <f t="shared" si="1"/>
-        <v>6514.22</v>
-      </c>
-      <c r="I17" s="227">
+      <c r="G17" s="193">
+        <v>6625.7280837479811</v>
+      </c>
+      <c r="I17" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="228"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="233"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="125">
         <v>4</v>
       </c>
       <c r="C18" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="129">
-        <v>6514.22</v>
+      <c r="E18" s="192">
+        <v>6625.7280837479811</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="130">
-        <f t="shared" si="1"/>
-        <v>6514.22</v>
-      </c>
-      <c r="I18" s="227">
+      <c r="G18" s="193">
+        <v>6625.7280837479811</v>
+      </c>
+      <c r="I18" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="228"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J18" s="233"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="126">
         <v>4</v>
       </c>
       <c r="C19" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="129">
-        <v>5329.82</v>
+      <c r="E19" s="192">
+        <v>5421.0502503392572</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="130">
-        <f t="shared" si="1"/>
-        <v>5329.82</v>
-      </c>
-      <c r="I19" s="227">
+      <c r="G19" s="193">
+        <v>5421.0502503392572</v>
+      </c>
+      <c r="I19" s="232">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="228"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J19" s="233"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="125"/>
       <c r="C20" s="125"/>
       <c r="E20" s="125"/>
       <c r="G20" s="128"/>
-      <c r="I20" s="227"/>
-      <c r="J20" s="228"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="151" t="s">
+      <c r="I20" s="232"/>
+      <c r="J20" s="233"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="149" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="151"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="153">
+      <c r="C21" s="149"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="151">
         <f>SUM(E5:E20)</f>
-        <v>200862.66000000003</v>
-      </c>
-      <c r="F21" s="154"/>
-      <c r="G21" s="153">
+        <v>180928.74722197096</v>
+      </c>
+      <c r="F21" s="152"/>
+      <c r="G21" s="151">
         <f>SUM(G5:G20)</f>
-        <v>76394.06</v>
-      </c>
-      <c r="I21" s="227">
+        <v>77701.720254862681</v>
+      </c>
+      <c r="I21" s="232">
         <f>E21-G21</f>
-        <v>124468.60000000003</v>
-      </c>
-      <c r="J21" s="228"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+        <v>103227.02696710828</v>
+      </c>
+      <c r="J21" s="233"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C22" s="125">
         <v>1</v>
       </c>
-      <c r="E22" s="134">
-        <v>690.9</v>
-      </c>
-      <c r="G22" s="135">
+      <c r="E22" s="194">
+        <v>702.72873615508888</v>
+      </c>
+      <c r="G22" s="133">
         <f>E22</f>
-        <v>690.9</v>
-      </c>
-      <c r="I22" s="227">
-        <f t="shared" ref="I22" si="2">E22-G22</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="228"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+        <v>702.72873615508888</v>
+      </c>
+      <c r="I22" s="232">
+        <f t="shared" ref="I22" si="1">E22-G22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="233"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="125">
         <v>2</v>
       </c>
-      <c r="E23" s="134">
-        <v>592.20000000000005</v>
-      </c>
-      <c r="G23" s="135">
-        <f t="shared" ref="G23:G29" si="3">E23</f>
-        <v>592.20000000000005</v>
-      </c>
-      <c r="I23" s="227">
-        <f t="shared" ref="I23:I31" si="4">E23-G23</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="228"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E23" s="194">
+        <v>602.33891670436185</v>
+      </c>
+      <c r="G23" s="133">
+        <f t="shared" ref="G23:G29" si="2">E23</f>
+        <v>602.33891670436185</v>
+      </c>
+      <c r="I23" s="232">
+        <f t="shared" ref="I23:I31" si="3">E23-G23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="233"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C24" s="125">
         <v>3</v>
       </c>
-      <c r="E24" s="134">
-        <v>592.20000000000005</v>
-      </c>
-      <c r="G24" s="135">
+      <c r="E24" s="194">
+        <v>602.33891670436185</v>
+      </c>
+      <c r="G24" s="133">
+        <f t="shared" si="2"/>
+        <v>602.33891670436185</v>
+      </c>
+      <c r="I24" s="232">
         <f t="shared" si="3"/>
-        <v>592.20000000000005</v>
-      </c>
-      <c r="I24" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="228"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="233"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C25" s="125">
         <v>4</v>
       </c>
-      <c r="E25" s="134">
-        <v>592.20000000000005</v>
-      </c>
-      <c r="G25" s="135">
+      <c r="E25" s="194">
+        <v>602.33891670436185</v>
+      </c>
+      <c r="G25" s="133">
+        <f t="shared" si="2"/>
+        <v>602.33891670436185</v>
+      </c>
+      <c r="I25" s="232">
         <f t="shared" si="3"/>
-        <v>592.20000000000005</v>
-      </c>
-      <c r="I25" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="228"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="233"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="125">
         <v>5</v>
       </c>
-      <c r="E26" s="134">
-        <v>592.20000000000005</v>
-      </c>
-      <c r="G26" s="135">
+      <c r="E26" s="194">
+        <v>602.33891670436185</v>
+      </c>
+      <c r="G26" s="133">
+        <f t="shared" si="2"/>
+        <v>602.33891670436185</v>
+      </c>
+      <c r="I26" s="232">
         <f t="shared" si="3"/>
-        <v>592.20000000000005</v>
-      </c>
-      <c r="I26" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="228"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="233"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C27" s="125">
         <v>6</v>
       </c>
-      <c r="E27" s="134">
-        <v>296.10000000000002</v>
-      </c>
-      <c r="G27" s="135">
+      <c r="E27" s="194">
+        <v>301.16945835218092</v>
+      </c>
+      <c r="G27" s="133">
+        <f t="shared" si="2"/>
+        <v>301.16945835218092</v>
+      </c>
+      <c r="I27" s="232">
         <f t="shared" si="3"/>
-        <v>296.10000000000002</v>
-      </c>
-      <c r="I27" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="228"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="233"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C28" s="125">
         <v>7</v>
       </c>
-      <c r="E28" s="134">
-        <v>296.10000000000002</v>
-      </c>
-      <c r="G28" s="135">
+      <c r="E28" s="194">
+        <v>301.16945835218092</v>
+      </c>
+      <c r="G28" s="133">
+        <f t="shared" si="2"/>
+        <v>301.16945835218092</v>
+      </c>
+      <c r="I28" s="232">
         <f t="shared" si="3"/>
-        <v>296.10000000000002</v>
-      </c>
-      <c r="I28" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="228"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="233"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="125" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="125">
         <v>8</v>
       </c>
-      <c r="E29" s="134">
-        <v>296.10000000000002</v>
-      </c>
-      <c r="G29" s="135">
+      <c r="E29" s="194">
+        <v>301.16945835218092</v>
+      </c>
+      <c r="G29" s="133">
+        <f t="shared" si="2"/>
+        <v>301.16945835218092</v>
+      </c>
+      <c r="I29" s="232">
         <f t="shared" si="3"/>
-        <v>296.10000000000002</v>
-      </c>
-      <c r="I29" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="228"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="156" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="233"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="154" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="157"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="153">
+      <c r="C30" s="155"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="151">
         <f>SUM(E22:E29)</f>
-        <v>3947.9999999999995</v>
-      </c>
-      <c r="F30" s="155"/>
-      <c r="G30" s="153">
+        <v>4015.592778029079</v>
+      </c>
+      <c r="F30" s="153"/>
+      <c r="G30" s="151">
         <f>SUM(G22:G29)</f>
-        <v>3947.9999999999995</v>
-      </c>
-      <c r="I30" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="228"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="133"/>
-      <c r="G31" s="130"/>
-      <c r="I31" s="227">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="228"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="131"/>
-      <c r="G32" s="132"/>
-      <c r="I32" s="227"/>
-      <c r="J32" s="228"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="133">
+        <v>4015.592778029079</v>
+      </c>
+      <c r="I30" s="232">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="233"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="132"/>
+      <c r="G31" s="129"/>
+      <c r="I31" s="232">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="233"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="130"/>
+      <c r="G32" s="131"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="233"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="132">
         <f>E30+E21</f>
-        <v>204810.66000000003</v>
-      </c>
-      <c r="G33" s="130">
+        <v>184944.34000000003</v>
+      </c>
+      <c r="G33" s="129">
         <f>G21+G30</f>
-        <v>80342.06</v>
-      </c>
-      <c r="I33" s="227">
+        <v>81717.313032891761</v>
+      </c>
+      <c r="I33" s="232">
         <f>E33-G33</f>
-        <v>124468.60000000003</v>
-      </c>
-      <c r="J33" s="228"/>
+        <v>103227.02696710826</v>
+      </c>
+      <c r="J33" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="31">

--- a/2026/SALTA 1167/Mayo/SALTA1167-Mayo.xlsx
+++ b/2026/SALTA 1167/Mayo/SALTA1167-Mayo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38AC16E-EA39-49B9-A52B-4AAADCAAD06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F1A4F4-0069-4F72-97BD-6D75541CECF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$103</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="150">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -419,30 +419,18 @@
     <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE SALTA 1167</t>
   </si>
   <si>
-    <t>Federacion patronal - Seguro silleteros</t>
-  </si>
-  <si>
-    <t>Transf 27/04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bonificado x EDESUR </t>
   </si>
   <si>
     <t>SUM</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>VTO 18/06</t>
   </si>
   <si>
     <t>PERÍODO: MAYO</t>
   </si>
   <si>
-    <t>Honorario administracion - Mes de MAYO</t>
-  </si>
-  <si>
     <t>Transf 06/05</t>
   </si>
   <si>
@@ -479,7 +467,25 @@
     <t>Easy Barracas - Compra de termotanque - Cuota 3  - Restan 3 cuotas de $157.988,29</t>
   </si>
   <si>
-    <t>Transf 29/05</t>
+    <t>FCI FIMA</t>
+  </si>
+  <si>
+    <t>Comision cuenta dolares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso 05/05 </t>
+  </si>
+  <si>
+    <t>SALDO TOTAL AL 29/5</t>
+  </si>
+  <si>
+    <t>Egreso a FCI FIMA</t>
+  </si>
+  <si>
+    <t>Honorario administracion - Mes de MAYO - Se transfirieron el 29/05 y no fueron incluidos en extracto bancario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajuste inflacionario de honorarios -  mes anterior no cobrado </t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1130,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1149,7 +1155,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1283,15 +1288,7 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1424,17 +1421,6 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1443,6 +1429,22 @@
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1965,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1982,36 +1984,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="197" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="200"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="198"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="67" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="18"/>
@@ -2023,10 +2025,10 @@
         <v>75</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C5" s="15"/>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="51" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="16"/>
@@ -2043,49 +2045,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="202" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="202"/>
+      <c r="B8" s="200" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="200"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="202"/>
-      <c r="C10" s="202"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="199" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="201"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
+      <c r="E13" s="199"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="201"/>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
+      <c r="A14" s="199"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
+      <c r="E14" s="199"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="201"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
+      <c r="A15" s="199"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
+      <c r="E15" s="199"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="201"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
+      <c r="A16" s="199"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
+      <c r="E16" s="199"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2102,35 +2104,35 @@
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="100"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="99"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="197" t="s">
+      <c r="A22" s="195" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="198"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="187">
+      <c r="B22" s="196"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="183">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="181" t="s">
-        <v>135</v>
-      </c>
-      <c r="H22" s="89"/>
+      <c r="E22" s="176" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="88"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="197"/>
-      <c r="B23" s="198"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="103"/>
-      <c r="H23" s="89"/>
+      <c r="A23" s="195"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="102"/>
+      <c r="H23" s="88"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
@@ -2138,267 +2140,263 @@
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="171">
+      <c r="D24" s="184"/>
+      <c r="E24" s="166">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="24" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="172"/>
+      <c r="D25" s="185"/>
+      <c r="E25" s="167"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="197" t="s">
+      <c r="A26" s="195" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="198"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="189">
+      <c r="B26" s="196"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="186">
         <v>75267</v>
       </c>
-      <c r="E26" s="170" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="121" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="122"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="185">
-        <v>29150</v>
-      </c>
-      <c r="E27" s="170" t="s">
-        <v>128</v>
+      <c r="E26" s="165" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="118">
+        <f>SUM(D26:D26)</f>
+        <v>75267</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="123">
-        <f>SUM(D26:D27)</f>
-        <v>104417</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
+      <c r="A28" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="101"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="113"/>
-      <c r="E29" s="173"/>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="100"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="187"/>
+      <c r="E28" s="168"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="188">
+        <v>0</v>
+      </c>
+      <c r="E29" s="176"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="104">
-        <v>0</v>
-      </c>
-      <c r="E30" s="181"/>
+      <c r="D30" s="188">
+        <v>6420.51</v>
+      </c>
+      <c r="E30" s="176" t="str">
+        <f>E31</f>
+        <v>Transf 05/05</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="5"/>
+      <c r="B31" s="115"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="186">
-        <v>6420.51</v>
-      </c>
-      <c r="E31" s="181" t="str">
-        <f>E32</f>
-        <v>Transf 05/05</v>
+      <c r="D31" s="188">
+        <v>330512.58</v>
+      </c>
+      <c r="E31" s="104" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="120"/>
+      <c r="A32" s="193" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="194"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="186">
-        <v>330512.58</v>
-      </c>
-      <c r="E32" s="105" t="s">
-        <v>138</v>
+      <c r="D32" s="188">
+        <v>193996.95</v>
+      </c>
+      <c r="E32" s="104" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="195" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="196"/>
+      <c r="A33" s="105" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="101"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="186">
-        <v>193996.95</v>
-      </c>
-      <c r="E33" s="105" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="106" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="102"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="186">
+      <c r="D33" s="188">
         <v>24915.01</v>
       </c>
-      <c r="E34" s="105" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="s">
+      <c r="E33" s="104" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
         <v>2</v>
       </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="189"/>
+      <c r="E34" s="169">
+        <f>SUM(D29:D33)</f>
+        <v>555845.05000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="174">
-        <f>SUM(D30:D34)</f>
-        <v>555845.05000000005</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="25"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="175"/>
-    </row>
-    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="197" t="s">
+      <c r="D35" s="184"/>
+      <c r="E35" s="170"/>
+    </row>
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="195" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="198"/>
+      <c r="B36" s="196"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="188">
+        <v>82000</v>
+      </c>
+      <c r="E36" s="104" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="195" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="196"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="186">
-        <v>82000</v>
-      </c>
-      <c r="E37" s="105" t="s">
+      <c r="D37" s="190">
+        <v>300000</v>
+      </c>
+      <c r="E37" s="104" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="175" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="197" t="s">
-        <v>144</v>
-      </c>
-      <c r="B38" s="198"/>
+      <c r="B38" s="117"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="188">
-        <v>300000</v>
-      </c>
-      <c r="E38" s="105" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="180" t="s">
-        <v>140</v>
-      </c>
-      <c r="B39" s="122"/>
+      <c r="D38" s="190">
+        <v>900000</v>
+      </c>
+      <c r="E38" s="104" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="195" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" s="196"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="188">
-        <v>900000</v>
-      </c>
-      <c r="E39" s="105" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="197" t="s">
+      <c r="D39" s="190">
+        <v>148155</v>
+      </c>
+      <c r="E39" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="B40" s="198"/>
+    </row>
+    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="116" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="117"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="188">
-        <v>148155</v>
-      </c>
-      <c r="E40" s="105" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="121" t="s">
+      <c r="D40" s="190">
+        <v>120000</v>
+      </c>
+      <c r="E40" s="104" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="195" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="122"/>
+      <c r="B41" s="196"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="188">
-        <v>120000</v>
-      </c>
-      <c r="E41" s="105" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="197" t="s">
-        <v>146</v>
-      </c>
-      <c r="B42" s="198"/>
+      <c r="D41" s="190">
+        <v>157988.29</v>
+      </c>
+      <c r="E41" s="104"/>
+    </row>
+    <row r="42" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="195"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="188">
-        <v>157988.29</v>
-      </c>
-      <c r="E42" s="105"/>
-    </row>
-    <row r="43" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="197"/>
-      <c r="B43" s="198"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="105"/>
+      <c r="D42" s="190"/>
+      <c r="E42" s="104"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="118">
+        <f>SUM(D36:D42)</f>
+        <v>1708143.29</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="123">
-        <f>SUM(D37:D43)</f>
-        <v>1708143.29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="A44" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="109"/>
-      <c r="E45" s="176"/>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="121" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="122"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="190">
-        <v>150000</v>
-      </c>
-      <c r="E46" s="177" t="s">
-        <v>147</v>
-      </c>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="191"/>
+      <c r="E44" s="171"/>
+    </row>
+    <row r="45" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="195" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" s="196"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="192">
+        <v>170000</v>
+      </c>
+      <c r="E45" s="172"/>
+    </row>
+    <row r="46" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="195" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" s="196"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="192">
+        <v>20000</v>
+      </c>
+      <c r="E46" s="172"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
@@ -2406,20 +2404,20 @@
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="171">
-        <f>SUM(D46:D46)</f>
-        <v>150000</v>
+      <c r="D47" s="109"/>
+      <c r="E47" s="166">
+        <f>SUM(D45:D46)</f>
+        <v>190000</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="48"/>
+      <c r="B48" s="47"/>
       <c r="C48" s="21"/>
-      <c r="D48" s="108"/>
-      <c r="E48" s="123"/>
+      <c r="D48" s="107"/>
+      <c r="E48" s="118"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -2427,395 +2425,444 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="191">
-        <v>0</v>
-      </c>
-      <c r="E49" s="178"/>
+      <c r="D49" s="103">
+        <v>69000</v>
+      </c>
+      <c r="E49" s="173"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="191">
-        <v>0</v>
-      </c>
-      <c r="E50" s="179"/>
+      <c r="D50" s="103">
+        <v>14125</v>
+      </c>
+      <c r="E50" s="173"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="103">
+        <f>66953.59-6952+140+10-6798</f>
+        <v>53353.59</v>
+      </c>
+      <c r="E51" s="174"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="123">
-        <f>SUM(D49:D50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="77"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="118">
+        <f>SUM(D49:D51)</f>
+        <v>136478.59</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="76"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="78"/>
-      <c r="E53" s="124"/>
-    </row>
-    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="30"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="119"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="1"/>
+      <c r="D55" s="78"/>
+      <c r="E55" s="79"/>
+      <c r="F55" s="29"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="82">
-        <f>(SUM(E21:E53))</f>
-        <v>3029252.19</v>
-      </c>
-      <c r="F55" s="99"/>
-      <c r="G55" s="30"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
-      <c r="H57" s="115"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
+      <c r="B56" s="8"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="81">
+        <f>(SUM(E21:E54))</f>
+        <v>3176580.78</v>
+      </c>
+      <c r="F56" s="98"/>
+      <c r="G56" s="29"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D58" s="78"/>
+      <c r="E58" s="78"/>
+      <c r="H58" s="110"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B58" s="10"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="84"/>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="73"/>
-      <c r="B59" s="102"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="72"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="83"/>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="205"/>
-      <c r="B60" s="205"/>
+      <c r="A60" s="72"/>
+      <c r="B60" s="101"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="104"/>
-      <c r="E60" s="72"/>
-    </row>
-    <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="71"/>
+    </row>
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="203"/>
+      <c r="B61" s="203"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="73"/>
-      <c r="B62" s="75"/>
+      <c r="D61" s="103"/>
+      <c r="E61" s="71"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="74"/>
-      <c r="E62" s="72"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="35"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41">
-        <f>SUM(D59:D62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="22" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="74"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="71"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="34"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40">
+        <f>SUM(D60:D63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="167"/>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="162"/>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="49">
-        <f>E63+E66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="69" t="s">
+      <c r="B69" s="8"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="48">
+        <f>E64+E67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="B70" s="70">
-        <f>E55</f>
-        <v>3029252.19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="69" t="s">
+      <c r="B71" s="69">
+        <f>E56</f>
+        <v>3176580.78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="70">
-        <f>E55-E53</f>
-        <v>3029252.19</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="69" t="s">
+      <c r="B72" s="69">
+        <f>E56-E54</f>
+        <v>3176580.78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="70">
-        <f>E68-E66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="69" t="s">
+      <c r="B73" s="69">
+        <f>E69-E67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="70">
-        <f>E68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="27"/>
-    </row>
-    <row r="76" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="91" t="s">
+      <c r="B74" s="69">
+        <f>E69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="26"/>
+    </row>
+    <row r="77" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="B76" s="134">
+      <c r="B77" s="129">
         <v>956980.3900000006</v>
       </c>
-      <c r="C76" s="27"/>
-      <c r="D76" s="33"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="40" t="s">
+      <c r="C77" s="26"/>
+      <c r="D77" s="32"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B77" s="96">
-        <f>-B71</f>
-        <v>-3029252.19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="40" t="s">
+      <c r="B78" s="95">
+        <f>-B72</f>
+        <v>-3176580.78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B78" s="96">
-        <f>B96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="40" t="s">
+      <c r="B79" s="95">
+        <f>B102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="97">
-        <f>PRORRATEO!G36-B86</f>
-        <v>2504691.1700000009</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="98" t="s">
+      <c r="B80" s="96">
+        <f>PRORRATEO!G36-B87</f>
+        <v>2511489.3800000008</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B80" s="116"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="94" t="s">
+      <c r="B81" s="111"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="B81" s="95">
-        <f>SUM(B76:C80)</f>
-        <v>432419.37000000151</v>
-      </c>
-      <c r="D81" s="30"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="92"/>
-      <c r="B82" s="92"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="29"/>
+      <c r="B82" s="94">
+        <f>SUM(B77:C81)</f>
+        <v>291888.99000000162</v>
+      </c>
+      <c r="D82" s="29"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="91" t="s">
+      <c r="A83" s="91"/>
+      <c r="B83" s="91"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="28"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="B83" s="134">
+      <c r="B84" s="129">
         <v>2000000</v>
       </c>
-      <c r="D83" s="29"/>
-      <c r="E83" s="30"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="40" t="s">
+      <c r="D84" s="28"/>
+      <c r="E84" s="29"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B84" s="96">
-        <f>-B72</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="40" t="s">
+      <c r="B85" s="95">
+        <f>-B73</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="29"/>
+      <c r="E85" s="29"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="96">
-        <f>B104</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="30"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="40" t="s">
+      <c r="B86" s="95">
+        <f>B110</f>
+        <v>0</v>
+      </c>
+      <c r="D86" s="29"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B86" s="97">
-        <v>0</v>
-      </c>
-      <c r="D86" s="168" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="98" t="s">
+      <c r="B87" s="96">
+        <v>0</v>
+      </c>
+      <c r="D87" s="163"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="B88" s="96">
+        <v>-1000000</v>
+      </c>
+      <c r="D88" s="163"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B87" s="116"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="94" t="s">
+      <c r="B89" s="111"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="B88" s="95">
-        <f>SUM(B83:C87)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="92"/>
-      <c r="B89" s="92"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="92"/>
-      <c r="B90" s="92"/>
-    </row>
-    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B90" s="94">
+        <f>SUM(B84:C89)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="91"/>
+      <c r="B91" s="91"/>
+    </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="204" t="s">
+      <c r="A92" s="91"/>
+      <c r="B92" s="91"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="90" t="s">
+        <v>143</v>
+      </c>
+      <c r="B93" s="129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B94" s="95">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="97"/>
+      <c r="B95" s="111"/>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="93" t="s">
+        <v>146</v>
+      </c>
+      <c r="B96" s="94">
+        <v>1010500.1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="202" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="204"/>
-      <c r="C92" s="204"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="204"/>
-      <c r="B93" s="204"/>
-      <c r="C93" s="204"/>
-    </row>
-    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="86"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26">
+      <c r="B98" s="202"/>
+      <c r="C98" s="202"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="202"/>
+      <c r="B99" s="202"/>
+      <c r="C99" s="202"/>
+    </row>
+    <row r="100" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="85"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25">
         <v>40000</v>
       </c>
-      <c r="E94" s="99"/>
-    </row>
-    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="86"/>
-      <c r="B95" s="88"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="99"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="31" t="s">
+      <c r="E100" s="98"/>
+    </row>
+    <row r="101" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="85"/>
+      <c r="B101" s="87"/>
+      <c r="C101" s="84"/>
+      <c r="D101" s="98"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B96" s="87">
-        <f>SUM(B94:B95)</f>
-        <v>0</v>
-      </c>
-      <c r="C96" s="32"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M97" s="6"/>
-    </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="203"/>
-      <c r="B98" s="203"/>
-      <c r="C98" s="203"/>
-      <c r="D98" s="203"/>
-      <c r="E98" s="203"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="203"/>
-      <c r="B99" s="203"/>
-      <c r="C99" s="203"/>
-      <c r="D99" s="203"/>
-      <c r="E99" s="203"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="203"/>
-      <c r="B100" s="203"/>
-      <c r="C100" s="203"/>
-      <c r="D100" s="203"/>
-      <c r="E100" s="203"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="203"/>
-      <c r="B101" s="203"/>
-      <c r="C101" s="203"/>
-      <c r="D101" s="203"/>
-      <c r="E101" s="203"/>
+      <c r="B102" s="86">
+        <f>SUM(B100:B101)</f>
+        <v>0</v>
+      </c>
+      <c r="C102" s="31"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M103" s="6"/>
+    </row>
+    <row r="104" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="201"/>
+      <c r="B104" s="201"/>
+      <c r="C104" s="201"/>
+      <c r="D104" s="201"/>
+      <c r="E104" s="201"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="201"/>
+      <c r="B105" s="201"/>
+      <c r="C105" s="201"/>
+      <c r="D105" s="201"/>
+      <c r="E105" s="201"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="201"/>
+      <c r="B106" s="201"/>
+      <c r="C106" s="201"/>
+      <c r="D106" s="201"/>
+      <c r="E106" s="201"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="201"/>
+      <c r="B107" s="201"/>
+      <c r="C107" s="201"/>
+      <c r="D107" s="201"/>
+      <c r="E107" s="201"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A98:E101"/>
-    <mergeCell ref="A92:C93"/>
-    <mergeCell ref="A60:B60"/>
+  <mergeCells count="17">
+    <mergeCell ref="A104:E107"/>
+    <mergeCell ref="A98:C99"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
@@ -2855,571 +2902,571 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="135"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="138"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="204"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="133"/>
     </row>
     <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139"/>
-      <c r="B2" s="140"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142" t="s">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="142"/>
-      <c r="G2" s="143">
-        <v>0</v>
-      </c>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142" t="s">
+      <c r="F2" s="137"/>
+      <c r="G2" s="138">
+        <v>0</v>
+      </c>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="144">
+      <c r="K2" s="139">
         <v>2400000</v>
       </c>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="147"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="142"/>
       <c r="Q2" s="20"/>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="139"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="145"/>
-      <c r="O3" s="146"/>
-      <c r="P3" s="147"/>
+      <c r="A3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="141"/>
+      <c r="P3" s="142"/>
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="217" t="s">
+      <c r="A4" s="215" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="218"/>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="218"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="218"/>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="219"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="M4" s="216"/>
+      <c r="N4" s="216"/>
+      <c r="O4" s="216"/>
+      <c r="P4" s="217"/>
       <c r="Q4" s="20"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="220"/>
-      <c r="B5" s="221"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="221"/>
-      <c r="E5" s="221"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="221"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="221"/>
-      <c r="K5" s="221"/>
-      <c r="L5" s="221"/>
-      <c r="M5" s="221"/>
-      <c r="N5" s="221"/>
-      <c r="O5" s="221"/>
-      <c r="P5" s="222"/>
+      <c r="A5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="219"/>
+      <c r="E5" s="219"/>
+      <c r="F5" s="219"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="219"/>
+      <c r="K5" s="219"/>
+      <c r="L5" s="219"/>
+      <c r="M5" s="219"/>
+      <c r="N5" s="219"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="220"/>
       <c r="Q5" s="20"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="220"/>
-      <c r="B6" s="221"/>
-      <c r="C6" s="221"/>
-      <c r="D6" s="221"/>
-      <c r="E6" s="221"/>
-      <c r="F6" s="221"/>
-      <c r="G6" s="221"/>
-      <c r="H6" s="221"/>
-      <c r="I6" s="221"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="221"/>
-      <c r="O6" s="221"/>
-      <c r="P6" s="222"/>
+      <c r="A6" s="218"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="219"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="219"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="219"/>
+      <c r="H6" s="219"/>
+      <c r="I6" s="219"/>
+      <c r="J6" s="219"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="219"/>
+      <c r="M6" s="219"/>
+      <c r="N6" s="219"/>
+      <c r="O6" s="219"/>
+      <c r="P6" s="220"/>
       <c r="Q6" s="20"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="220"/>
-      <c r="B7" s="221"/>
-      <c r="C7" s="221"/>
-      <c r="D7" s="221"/>
-      <c r="E7" s="221"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="221"/>
-      <c r="H7" s="221"/>
-      <c r="I7" s="221"/>
-      <c r="J7" s="221"/>
-      <c r="K7" s="221"/>
-      <c r="L7" s="221"/>
-      <c r="M7" s="221"/>
-      <c r="N7" s="221"/>
-      <c r="O7" s="221"/>
-      <c r="P7" s="222"/>
+      <c r="A7" s="218"/>
+      <c r="B7" s="219"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="219"/>
+      <c r="E7" s="219"/>
+      <c r="F7" s="219"/>
+      <c r="G7" s="219"/>
+      <c r="H7" s="219"/>
+      <c r="I7" s="219"/>
+      <c r="J7" s="219"/>
+      <c r="K7" s="219"/>
+      <c r="L7" s="219"/>
+      <c r="M7" s="219"/>
+      <c r="N7" s="219"/>
+      <c r="O7" s="219"/>
+      <c r="P7" s="220"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="223"/>
-      <c r="B8" s="224"/>
-      <c r="C8" s="224"/>
-      <c r="D8" s="224"/>
-      <c r="E8" s="224"/>
-      <c r="F8" s="224"/>
-      <c r="G8" s="224"/>
-      <c r="H8" s="224"/>
-      <c r="I8" s="224"/>
-      <c r="J8" s="224"/>
-      <c r="K8" s="224"/>
-      <c r="L8" s="224"/>
-      <c r="M8" s="224"/>
-      <c r="N8" s="224"/>
-      <c r="O8" s="224"/>
-      <c r="P8" s="225"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="222"/>
+      <c r="D8" s="222"/>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="222"/>
+      <c r="K8" s="222"/>
+      <c r="L8" s="222"/>
+      <c r="M8" s="222"/>
+      <c r="N8" s="222"/>
+      <c r="O8" s="222"/>
+      <c r="P8" s="223"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="228" t="s">
+      <c r="A9" s="226" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="229"/>
-      <c r="C9" s="229"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="229"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="229"/>
-      <c r="P9" s="229"/>
+      <c r="B9" s="227"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="227"/>
+      <c r="H9" s="227"/>
+      <c r="I9" s="227"/>
+      <c r="J9" s="227"/>
+      <c r="K9" s="227"/>
+      <c r="L9" s="227"/>
+      <c r="M9" s="227"/>
+      <c r="N9" s="227"/>
+      <c r="O9" s="227"/>
+      <c r="P9" s="227"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="230" t="s">
+      <c r="A10" s="228" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="230"/>
-      <c r="C10" s="230"/>
-      <c r="D10" s="230"/>
-      <c r="E10" s="230"/>
-      <c r="F10" s="230"/>
-      <c r="G10" s="230"/>
-      <c r="H10" s="230"/>
-      <c r="I10" s="230"/>
-      <c r="J10" s="230"/>
-      <c r="K10" s="230"/>
-      <c r="L10" s="230"/>
-      <c r="M10" s="230"/>
-      <c r="N10" s="230"/>
-      <c r="O10" s="230"/>
-      <c r="P10" s="230"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="228"/>
+      <c r="I10" s="228"/>
+      <c r="J10" s="228"/>
+      <c r="K10" s="228"/>
+      <c r="L10" s="228"/>
+      <c r="M10" s="228"/>
+      <c r="N10" s="228"/>
+      <c r="O10" s="228"/>
+      <c r="P10" s="228"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="211" t="s">
+      <c r="A11" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="211" t="s">
+      <c r="B11" s="112"/>
+      <c r="C11" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="211" t="s">
+      <c r="D11" s="209" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="211" t="s">
+      <c r="E11" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="207" t="s">
+      <c r="F11" s="205" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="211" t="s">
+      <c r="G11" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="213" t="s">
+      <c r="H11" s="211" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="207" t="s">
+      <c r="I11" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="207" t="s">
+      <c r="J11" s="205" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="215" t="s">
+      <c r="K11" s="213" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="207" t="s">
+      <c r="L11" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="207" t="s">
-        <v>130</v>
-      </c>
-      <c r="N11" s="44" t="s">
+      <c r="M11" s="205" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="209" t="s">
+      <c r="O11" s="207" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="226" t="s">
+      <c r="P11" s="224" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="212"/>
-      <c r="B12" s="118"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="208"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="214"/>
-      <c r="I12" s="208"/>
-      <c r="J12" s="208"/>
-      <c r="K12" s="216"/>
-      <c r="L12" s="208"/>
-      <c r="M12" s="208"/>
-      <c r="N12" s="42" t="str">
+      <c r="A12" s="210"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="210"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="210"/>
+      <c r="F12" s="206"/>
+      <c r="G12" s="210"/>
+      <c r="H12" s="212"/>
+      <c r="I12" s="206"/>
+      <c r="J12" s="206"/>
+      <c r="K12" s="214"/>
+      <c r="L12" s="206"/>
+      <c r="M12" s="206"/>
+      <c r="N12" s="41" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O12" s="210"/>
-      <c r="P12" s="227"/>
+      <c r="O12" s="208"/>
+      <c r="P12" s="225"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45">
+      <c r="A13" s="44">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="54">
+      <c r="D13" s="44"/>
+      <c r="E13" s="53">
         <v>12</v>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="54">
         <v>264000.01</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="55">
         <f>F13</f>
         <v>264000.01</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="56">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
         <v>0</v>
       </c>
-      <c r="I13" s="57">
+      <c r="I13" s="56">
         <f>IF(H13&gt;0,H13*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="107">
+      <c r="J13" s="106">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
         <v>288000</v>
       </c>
-      <c r="K13" s="107">
+      <c r="K13" s="106">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="166">
+      <c r="L13" s="161">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="M13" s="183"/>
-      <c r="N13" s="165">
+      <c r="M13" s="178"/>
+      <c r="N13" s="160">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
         <v>288000.01</v>
       </c>
-      <c r="O13" s="58">
+      <c r="O13" s="57">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
         <v>305280.01</v>
       </c>
-      <c r="P13" s="59">
+      <c r="P13" s="58">
         <f>ROUND(N13*3%,0) + N13</f>
         <v>296640.01</v>
       </c>
-      <c r="Q13" s="30">
+      <c r="Q13" s="29">
         <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="158">
+      <c r="A14" s="153">
         <v>2</v>
       </c>
-      <c r="B14" s="158" t="s">
+      <c r="B14" s="153" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="158" t="s">
+      <c r="C14" s="153" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="159"/>
-      <c r="E14" s="160">
+      <c r="D14" s="154"/>
+      <c r="E14" s="155">
         <v>6.6</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="55">
         <v>179889.02</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="55">
         <v>180000</v>
       </c>
-      <c r="H14" s="161">
+      <c r="H14" s="156">
         <f t="shared" si="0"/>
         <v>-110.98000000001048</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="156">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="157">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="157">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="164">
         <f>EDESUR!I6</f>
         <v>31125.624497318255</v>
       </c>
-      <c r="M14" s="184"/>
-      <c r="N14" s="165">
+      <c r="M14" s="179"/>
+      <c r="N14" s="160">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
         <v>189415.02</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="158">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
         <v>200780.02</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="159">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
         <v>195097.02</v>
       </c>
-      <c r="Q14" s="30">
+      <c r="Q14" s="29">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45">
+      <c r="A15" s="44">
         <v>3</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="53">
         <v>5.4</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="54">
         <v>188075.03</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="55">
         <f>F15</f>
         <v>188075.03</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H15" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="107">
+      <c r="J15" s="106">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K15" s="107">
+      <c r="K15" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="166">
+      <c r="L15" s="161">
         <f>EDESUR!I7</f>
         <v>5421.0502503392572</v>
       </c>
-      <c r="M15" s="182"/>
-      <c r="N15" s="165">
+      <c r="M15" s="177"/>
+      <c r="N15" s="160">
         <f t="shared" si="4"/>
         <v>135021.03</v>
       </c>
-      <c r="O15" s="58">
+      <c r="O15" s="57">
         <f t="shared" si="5"/>
         <v>143122.03</v>
       </c>
-      <c r="P15" s="59">
+      <c r="P15" s="58">
         <f t="shared" si="6"/>
         <v>139072.03</v>
       </c>
-      <c r="Q15" s="30">
+      <c r="Q15" s="29">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="45">
+      <c r="A16" s="44">
         <v>4</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="53">
         <v>6.6</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="54">
         <v>145200.04</v>
       </c>
-      <c r="G16" s="56">
+      <c r="G16" s="55">
         <f>158400.2-G32</f>
         <v>145200</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="56">
         <f t="shared" si="0"/>
         <v>4.0000000008149073E-2</v>
       </c>
-      <c r="I16" s="57">
+      <c r="I16" s="56">
         <f t="shared" si="3"/>
         <v>1.2000000002444721E-3</v>
       </c>
-      <c r="J16" s="107">
+      <c r="J16" s="106">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K16" s="107">
+      <c r="K16" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="166">
+      <c r="L16" s="161">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="M16" s="183"/>
-      <c r="N16" s="165">
+      <c r="M16" s="178"/>
+      <c r="N16" s="160">
         <f t="shared" si="4"/>
         <v>158400.04</v>
       </c>
-      <c r="O16" s="58">
+      <c r="O16" s="57">
         <f t="shared" si="5"/>
         <v>167904.04</v>
       </c>
-      <c r="P16" s="59">
+      <c r="P16" s="58">
         <f t="shared" si="6"/>
         <v>163152.04</v>
       </c>
-      <c r="Q16" s="30">
+      <c r="Q16" s="29">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158">
+      <c r="A17" s="153">
         <v>5</v>
       </c>
-      <c r="B17" s="158" t="s">
+      <c r="B17" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="158" t="s">
+      <c r="C17" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="158" t="s">
+      <c r="D17" s="153" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="160">
+      <c r="E17" s="155">
         <v>6.6</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="55">
         <v>145200.04999999999</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="55">
         <f>F17</f>
         <v>145200.04999999999</v>
       </c>
-      <c r="H17" s="161">
+      <c r="H17" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="161">
+      <c r="I17" s="156">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="162">
+      <c r="J17" s="157">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K17" s="162">
+      <c r="K17" s="157">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="169">
+      <c r="L17" s="164">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="M17" s="184">
-        <v>50000</v>
-      </c>
-      <c r="N17" s="165">
+      <c r="M17" s="179">
+        <v>0</v>
+      </c>
+      <c r="N17" s="160">
         <f t="shared" si="4"/>
-        <v>208400.05</v>
-      </c>
-      <c r="O17" s="163">
+        <v>158400.04999999999</v>
+      </c>
+      <c r="O17" s="158">
         <f t="shared" si="5"/>
-        <v>220904.05</v>
-      </c>
-      <c r="P17" s="164">
+        <v>167904.05</v>
+      </c>
+      <c r="P17" s="159">
         <f t="shared" si="6"/>
-        <v>214652.05</v>
-      </c>
-      <c r="Q17" s="30">
+        <v>163152.04999999999</v>
+      </c>
+      <c r="Q17" s="29">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
@@ -3428,365 +3475,365 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="45">
+      <c r="A18" s="44">
         <v>6</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="53">
         <v>5.4</v>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="54">
         <v>118800.06</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="55">
         <f t="shared" ref="G18" si="8">F18</f>
         <v>118800.06</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="57">
+      <c r="I18" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="107">
+      <c r="J18" s="106">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K18" s="107">
+      <c r="K18" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="166">
+      <c r="L18" s="161">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="M18" s="183"/>
-      <c r="N18" s="165">
+      <c r="M18" s="178"/>
+      <c r="N18" s="160">
         <f t="shared" si="4"/>
         <v>129600.06</v>
       </c>
-      <c r="O18" s="58">
+      <c r="O18" s="57">
         <f t="shared" si="5"/>
         <v>137376.06</v>
       </c>
-      <c r="P18" s="59">
+      <c r="P18" s="58">
         <f t="shared" si="6"/>
         <v>133488.06</v>
       </c>
-      <c r="Q18" s="30">
+      <c r="Q18" s="29">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="158">
+      <c r="A19" s="153">
         <v>7</v>
       </c>
-      <c r="B19" s="158" t="s">
+      <c r="B19" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="158" t="s">
+      <c r="C19" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="158" t="s">
+      <c r="D19" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="160">
+      <c r="E19" s="155">
         <v>5.4</v>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="55">
         <v>122364.07</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="55">
         <f>F19</f>
         <v>122364.07</v>
       </c>
-      <c r="H19" s="161">
+      <c r="H19" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="161">
+      <c r="I19" s="156">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="162">
+      <c r="J19" s="157">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K19" s="162">
+      <c r="K19" s="157">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="166">
+      <c r="L19" s="161">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M19" s="183"/>
-      <c r="N19" s="165">
+      <c r="M19" s="178"/>
+      <c r="N19" s="160">
         <f t="shared" si="4"/>
         <v>129600.07</v>
       </c>
-      <c r="O19" s="163">
+      <c r="O19" s="158">
         <f t="shared" si="5"/>
         <v>137376.07</v>
       </c>
-      <c r="P19" s="164">
+      <c r="P19" s="159">
         <f t="shared" si="6"/>
         <v>133488.07</v>
       </c>
-      <c r="Q19" s="30">
+      <c r="Q19" s="29">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="158">
+      <c r="A20" s="153">
         <v>8</v>
       </c>
-      <c r="B20" s="158" t="s">
+      <c r="B20" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="158" t="s">
+      <c r="C20" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="159" t="s">
+      <c r="D20" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="160">
+      <c r="E20" s="155">
         <v>6.6</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="55">
         <v>222130.08</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="55">
         <f>F20</f>
         <v>222130.08</v>
       </c>
-      <c r="H20" s="161">
+      <c r="H20" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="161">
+      <c r="I20" s="156">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="162">
+      <c r="J20" s="157">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K20" s="162">
+      <c r="K20" s="157">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="166">
+      <c r="L20" s="161">
         <f>EDESUR!I13</f>
         <v>66680.352219450724</v>
       </c>
-      <c r="M20" s="183"/>
-      <c r="N20" s="165">
+      <c r="M20" s="178"/>
+      <c r="N20" s="160">
         <f t="shared" si="4"/>
         <v>225080.08</v>
       </c>
-      <c r="O20" s="163">
+      <c r="O20" s="158">
         <f t="shared" si="5"/>
         <v>238585.08</v>
       </c>
-      <c r="P20" s="164">
+      <c r="P20" s="159">
         <f t="shared" si="6"/>
         <v>231832.08</v>
       </c>
-      <c r="Q20" s="30">
+      <c r="Q20" s="29">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="45">
+      <c r="A21" s="44">
         <v>9</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="53">
         <v>6.6</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="54">
         <v>106012.09</v>
       </c>
-      <c r="G21" s="56">
-        <f>F21</f>
-        <v>106012.09</v>
-      </c>
-      <c r="H21" s="57">
+      <c r="G21" s="55">
+        <f>F21+28387</f>
+        <v>134399.09</v>
+      </c>
+      <c r="H21" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="57">
+        <v>-28387</v>
+      </c>
+      <c r="I21" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="107">
+      <c r="J21" s="106">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K21" s="107">
+      <c r="K21" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="166">
+      <c r="L21" s="161">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="183"/>
-      <c r="N21" s="165">
+      <c r="M21" s="178"/>
+      <c r="N21" s="160">
         <f t="shared" si="4"/>
-        <v>158400.09</v>
-      </c>
-      <c r="O21" s="58">
+        <v>130013.09</v>
+      </c>
+      <c r="O21" s="57">
         <f t="shared" si="5"/>
-        <v>167904.09</v>
-      </c>
-      <c r="P21" s="59">
+        <v>137814.09</v>
+      </c>
+      <c r="P21" s="58">
         <f t="shared" si="6"/>
-        <v>163152.09</v>
-      </c>
-      <c r="Q21" s="30">
+        <v>133913.09</v>
+      </c>
+      <c r="Q21" s="29">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="45">
+      <c r="A22" s="44">
         <v>10</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="53">
         <v>5.4</v>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="54">
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="G22" s="56">
-        <f>RESUMEN!D42</f>
-        <v>157988.29</v>
-      </c>
-      <c r="H22" s="57">
+      <c r="G22" s="55">
+        <f>RESUMEN!D41-28387</f>
+        <v>129601.29000000001</v>
+      </c>
+      <c r="H22" s="56">
         <f>F22-G22</f>
-        <v>-157988.19</v>
-      </c>
-      <c r="I22" s="57">
+        <v>-129601.19</v>
+      </c>
+      <c r="I22" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="107">
+      <c r="J22" s="106">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K22" s="107">
+      <c r="K22" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="166">
+      <c r="L22" s="161">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="M22" s="183"/>
-      <c r="N22" s="165">
+      <c r="M22" s="178"/>
+      <c r="N22" s="160">
         <f t="shared" si="4"/>
-        <v>-28387.9</v>
-      </c>
-      <c r="O22" s="58">
+        <v>-0.9</v>
+      </c>
+      <c r="O22" s="57">
         <f t="shared" si="5"/>
-        <v>-30090.9</v>
-      </c>
-      <c r="P22" s="59">
+        <v>-0.9</v>
+      </c>
+      <c r="P22" s="58">
         <f t="shared" si="6"/>
-        <v>-29239.9</v>
-      </c>
-      <c r="Q22" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="Q22" s="29">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45">
+      <c r="A23" s="44">
         <v>11</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="54">
+      <c r="D23" s="45"/>
+      <c r="E23" s="53">
         <v>5.4</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="54">
         <v>118800.11</v>
       </c>
-      <c r="G23" s="56">
+      <c r="G23" s="55">
         <f>125400-G34</f>
         <v>118799.78</v>
       </c>
-      <c r="H23" s="57">
+      <c r="H23" s="56">
         <f t="shared" si="0"/>
         <v>0.33000000000174623</v>
       </c>
-      <c r="I23" s="57">
+      <c r="I23" s="56">
         <f t="shared" si="3"/>
         <v>9.900000000052386E-3</v>
       </c>
-      <c r="J23" s="107">
+      <c r="J23" s="106">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K23" s="107">
+      <c r="K23" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="166">
+      <c r="L23" s="161">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M23" s="183"/>
-      <c r="N23" s="165">
+      <c r="M23" s="178"/>
+      <c r="N23" s="160">
         <f t="shared" si="4"/>
         <v>129600.11</v>
       </c>
-      <c r="O23" s="58">
+      <c r="O23" s="57">
         <f t="shared" si="5"/>
         <v>137376.10999999999</v>
       </c>
-      <c r="P23" s="59">
+      <c r="P23" s="58">
         <f t="shared" si="6"/>
         <v>133488.10999999999</v>
       </c>
-      <c r="Q23" s="30">
+      <c r="Q23" s="29">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
@@ -3795,848 +3842,848 @@
       </c>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="45">
+      <c r="A24" s="44">
         <v>12</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="53">
         <v>6.6</v>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="54">
         <v>145200.12</v>
       </c>
-      <c r="G24" s="56">
+      <c r="G24" s="55">
         <f>F24</f>
         <v>145200.12</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="57">
+      <c r="I24" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="107">
+      <c r="J24" s="106">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K24" s="107">
+      <c r="K24" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="166">
+      <c r="L24" s="161">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="M24" s="183"/>
-      <c r="N24" s="165">
+      <c r="M24" s="178"/>
+      <c r="N24" s="160">
         <f t="shared" si="4"/>
         <v>158400.12</v>
       </c>
-      <c r="O24" s="58">
+      <c r="O24" s="57">
         <f t="shared" si="5"/>
         <v>167904.12</v>
       </c>
-      <c r="P24" s="59">
+      <c r="P24" s="58">
         <f t="shared" si="6"/>
         <v>163152.12</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="29">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="45">
+      <c r="A25" s="44">
         <v>13</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="C25" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="53">
         <v>6.6</v>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="54">
         <v>145200.13</v>
       </c>
-      <c r="G25" s="56">
+      <c r="G25" s="55">
         <v>149556.13</v>
       </c>
-      <c r="H25" s="57">
+      <c r="H25" s="56">
         <f t="shared" si="0"/>
         <v>-4356</v>
       </c>
-      <c r="I25" s="57">
+      <c r="I25" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="107">
+      <c r="J25" s="106">
         <f t="shared" si="1"/>
         <v>158400</v>
       </c>
-      <c r="K25" s="107">
+      <c r="K25" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="166">
+      <c r="L25" s="161">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="M25" s="183"/>
-      <c r="N25" s="165">
+      <c r="M25" s="178"/>
+      <c r="N25" s="160">
         <f t="shared" si="4"/>
         <v>154044.13</v>
       </c>
-      <c r="O25" s="58">
+      <c r="O25" s="57">
         <f t="shared" si="5"/>
         <v>163287.13</v>
       </c>
-      <c r="P25" s="59">
+      <c r="P25" s="58">
         <f t="shared" si="6"/>
         <v>158665.13</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="29">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="158">
+      <c r="A26" s="153">
         <v>14</v>
       </c>
-      <c r="B26" s="158" t="s">
+      <c r="B26" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="158" t="s">
+      <c r="C26" s="153" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="159"/>
-      <c r="E26" s="160">
+      <c r="D26" s="154"/>
+      <c r="E26" s="155">
         <v>5.4</v>
       </c>
-      <c r="F26" s="56">
+      <c r="F26" s="55">
         <v>118800.14</v>
       </c>
-      <c r="G26" s="56">
+      <c r="G26" s="55">
         <f>F26</f>
         <v>118800.14</v>
       </c>
-      <c r="H26" s="161">
+      <c r="H26" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="161">
+      <c r="I26" s="156">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="162">
+      <c r="J26" s="157">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K26" s="162">
+      <c r="K26" s="157">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="169">
+      <c r="L26" s="164">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="M26" s="184"/>
-      <c r="N26" s="165">
+      <c r="M26" s="179"/>
+      <c r="N26" s="160">
         <f t="shared" si="4"/>
         <v>129600.14</v>
       </c>
-      <c r="O26" s="163">
+      <c r="O26" s="158">
         <f t="shared" si="5"/>
         <v>137376.14000000001</v>
       </c>
-      <c r="P26" s="164">
+      <c r="P26" s="159">
         <f t="shared" si="6"/>
         <v>133488.14000000001</v>
       </c>
-      <c r="Q26" s="30">
+      <c r="Q26" s="29">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45">
+      <c r="A27" s="44">
         <v>15</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="54">
+      <c r="D27" s="45"/>
+      <c r="E27" s="53">
         <v>5.4</v>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="54">
         <v>241164.15</v>
       </c>
-      <c r="G27" s="56">
+      <c r="G27" s="55">
         <f>F27</f>
         <v>241164.15</v>
       </c>
-      <c r="H27" s="57">
+      <c r="H27" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="57">
+      <c r="I27" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="107">
+      <c r="J27" s="106">
         <f t="shared" si="1"/>
         <v>129600</v>
       </c>
-      <c r="K27" s="107">
+      <c r="K27" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="166">
+      <c r="L27" s="161">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="M27" s="183"/>
-      <c r="N27" s="165">
+      <c r="M27" s="178"/>
+      <c r="N27" s="160">
         <f t="shared" si="4"/>
         <v>129600.15</v>
       </c>
-      <c r="O27" s="58">
+      <c r="O27" s="57">
         <f t="shared" si="5"/>
         <v>137376.15</v>
       </c>
-      <c r="P27" s="59">
+      <c r="P27" s="58">
         <f t="shared" si="6"/>
         <v>133488.15</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="29">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="45">
+      <c r="A28" s="44">
         <v>16</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="45" t="s">
+      <c r="C28" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="53">
         <v>0.7</v>
       </c>
-      <c r="F28" s="55">
+      <c r="F28" s="54">
         <v>15400.16</v>
       </c>
-      <c r="G28" s="56">
+      <c r="G28" s="55">
         <f t="shared" ref="G28:G34" si="9">F28</f>
         <v>15400.16</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="57">
+      <c r="I28" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="107">
+      <c r="J28" s="106">
         <f t="shared" si="1"/>
         <v>16800</v>
       </c>
-      <c r="K28" s="107">
+      <c r="K28" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="166">
+      <c r="L28" s="161">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="M28" s="183"/>
-      <c r="N28" s="165">
+      <c r="M28" s="178"/>
+      <c r="N28" s="160">
         <f t="shared" si="4"/>
         <v>16800.16</v>
       </c>
-      <c r="O28" s="58">
+      <c r="O28" s="57">
         <f t="shared" si="5"/>
         <v>17808.16</v>
       </c>
-      <c r="P28" s="59">
+      <c r="P28" s="58">
         <f t="shared" si="6"/>
         <v>17304.16</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="29">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="45">
+      <c r="A29" s="44">
         <v>17</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="46"/>
-      <c r="E29" s="54">
+      <c r="D29" s="45"/>
+      <c r="E29" s="53">
         <v>0.6</v>
       </c>
-      <c r="F29" s="56">
+      <c r="F29" s="55">
         <v>13200.17</v>
       </c>
-      <c r="G29" s="56">
+      <c r="G29" s="55">
         <v>26400.17</v>
       </c>
-      <c r="H29" s="57">
+      <c r="H29" s="56">
         <f t="shared" si="0"/>
         <v>-13199.999999999998</v>
       </c>
-      <c r="I29" s="57">
+      <c r="I29" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="107">
+      <c r="J29" s="106">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
-      <c r="K29" s="107">
+      <c r="K29" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="166">
+      <c r="L29" s="161">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="M29" s="183"/>
-      <c r="N29" s="165">
+      <c r="M29" s="178"/>
+      <c r="N29" s="160">
         <f t="shared" si="4"/>
         <v>1200.17</v>
       </c>
-      <c r="O29" s="58">
+      <c r="O29" s="57">
         <f t="shared" si="5"/>
         <v>1272.17</v>
       </c>
-      <c r="P29" s="59">
+      <c r="P29" s="58">
         <f t="shared" si="6"/>
         <v>1236.17</v>
       </c>
-      <c r="Q29" s="30">
+      <c r="Q29" s="29">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="45">
+      <c r="A30" s="44">
         <v>18</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="C30" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="90"/>
-      <c r="E30" s="54">
+      <c r="D30" s="89"/>
+      <c r="E30" s="53">
         <v>0.6</v>
       </c>
-      <c r="F30" s="55">
+      <c r="F30" s="54">
         <v>13200.18</v>
       </c>
-      <c r="G30" s="56">
-        <v>0</v>
-      </c>
-      <c r="H30" s="57">
+      <c r="G30" s="55">
+        <v>0</v>
+      </c>
+      <c r="H30" s="56">
         <f t="shared" si="0"/>
         <v>13200.18</v>
       </c>
-      <c r="I30" s="57">
+      <c r="I30" s="56">
         <f t="shared" si="3"/>
         <v>396.00540000000001</v>
       </c>
-      <c r="J30" s="107">
+      <c r="J30" s="106">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
-      <c r="K30" s="107">
+      <c r="K30" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="166">
+      <c r="L30" s="161">
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="M30" s="183"/>
-      <c r="N30" s="165">
+      <c r="M30" s="178"/>
+      <c r="N30" s="160">
         <f t="shared" si="4"/>
         <v>27996.18</v>
       </c>
-      <c r="O30" s="58">
+      <c r="O30" s="57">
         <f t="shared" si="5"/>
         <v>29676.18</v>
       </c>
-      <c r="P30" s="59">
+      <c r="P30" s="58">
         <f t="shared" si="6"/>
         <v>28836.18</v>
       </c>
-      <c r="Q30" s="30">
+      <c r="Q30" s="29">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="158">
+      <c r="A31" s="153">
         <v>19</v>
       </c>
-      <c r="B31" s="158" t="s">
+      <c r="B31" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="158" t="s">
+      <c r="C31" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="159"/>
-      <c r="E31" s="160">
+      <c r="D31" s="154"/>
+      <c r="E31" s="155">
         <v>0.6</v>
       </c>
-      <c r="F31" s="56">
+      <c r="F31" s="55">
         <v>13200.19</v>
       </c>
-      <c r="G31" s="56">
+      <c r="G31" s="55">
         <f>F31</f>
         <v>13200.19</v>
       </c>
-      <c r="H31" s="161">
+      <c r="H31" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="161">
+      <c r="I31" s="156">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="162">
+      <c r="J31" s="157">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
-      <c r="K31" s="162">
+      <c r="K31" s="157">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="169">
+      <c r="L31" s="164">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="M31" s="184"/>
-      <c r="N31" s="165">
+      <c r="M31" s="179"/>
+      <c r="N31" s="160">
         <f t="shared" si="4"/>
         <v>14400.19</v>
       </c>
-      <c r="O31" s="163"/>
-      <c r="P31" s="164">
+      <c r="O31" s="158"/>
+      <c r="P31" s="159">
         <f t="shared" si="6"/>
         <v>14832.19</v>
       </c>
-      <c r="Q31" s="30">
+      <c r="Q31" s="29">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="60">
+      <c r="A32" s="59">
         <v>20</v>
       </c>
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="54">
+      <c r="E32" s="53">
         <v>0.6</v>
       </c>
-      <c r="F32" s="62">
+      <c r="F32" s="61">
         <v>13200.2</v>
       </c>
-      <c r="G32" s="56">
+      <c r="G32" s="55">
         <f>F32</f>
         <v>13200.2</v>
       </c>
-      <c r="H32" s="57">
+      <c r="H32" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="57">
+      <c r="I32" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J32" s="107">
+      <c r="J32" s="106">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
-      <c r="K32" s="107">
+      <c r="K32" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="166">
+      <c r="L32" s="161">
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="M32" s="183"/>
-      <c r="N32" s="165">
+      <c r="M32" s="178"/>
+      <c r="N32" s="160">
         <f t="shared" si="4"/>
         <v>14400.2</v>
       </c>
-      <c r="O32" s="58"/>
-      <c r="P32" s="59">
+      <c r="O32" s="57"/>
+      <c r="P32" s="58">
         <f t="shared" si="6"/>
         <v>14832.2</v>
       </c>
-      <c r="Q32" s="30">
+      <c r="Q32" s="29">
         <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="60">
+      <c r="A33" s="59">
         <v>21</v>
       </c>
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="54">
+      <c r="E33" s="53">
         <v>0.3</v>
       </c>
-      <c r="F33" s="62">
+      <c r="F33" s="61">
         <v>6600.21</v>
       </c>
-      <c r="G33" s="56">
-        <v>0</v>
-      </c>
-      <c r="H33" s="57">
+      <c r="G33" s="55">
+        <v>6798.21</v>
+      </c>
+      <c r="H33" s="56">
         <f t="shared" si="0"/>
-        <v>6600.21</v>
-      </c>
-      <c r="I33" s="57">
+        <v>-198</v>
+      </c>
+      <c r="I33" s="56">
         <f t="shared" si="3"/>
-        <v>198.00629999999998</v>
-      </c>
-      <c r="J33" s="107">
+        <v>0</v>
+      </c>
+      <c r="J33" s="106">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="K33" s="107">
+      <c r="K33" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="166">
+      <c r="L33" s="161">
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="M33" s="183"/>
-      <c r="N33" s="165">
+      <c r="M33" s="178"/>
+      <c r="N33" s="160">
         <f t="shared" si="4"/>
-        <v>13998.21</v>
-      </c>
-      <c r="O33" s="58"/>
-      <c r="P33" s="59">
+        <v>7002.21</v>
+      </c>
+      <c r="O33" s="57"/>
+      <c r="P33" s="58">
         <f t="shared" si="6"/>
-        <v>14418.21</v>
-      </c>
-      <c r="Q33" s="30">
+        <v>7212.21</v>
+      </c>
+      <c r="Q33" s="29">
         <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="61">
+      <c r="A34" s="60">
         <v>22</v>
       </c>
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="45" t="s">
+      <c r="C34" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="46"/>
-      <c r="E34" s="54">
+      <c r="D34" s="45"/>
+      <c r="E34" s="53">
         <v>0.3</v>
       </c>
-      <c r="F34" s="62">
+      <c r="F34" s="61">
         <v>6600.22</v>
       </c>
-      <c r="G34" s="157">
+      <c r="G34" s="152">
         <f t="shared" si="9"/>
         <v>6600.22</v>
       </c>
-      <c r="H34" s="57">
+      <c r="H34" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="57">
+      <c r="I34" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J34" s="107">
+      <c r="J34" s="106">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="K34" s="107">
+      <c r="K34" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="166">
+      <c r="L34" s="161">
         <f>EDESUR!I28</f>
         <v>0</v>
       </c>
-      <c r="M34" s="183"/>
-      <c r="N34" s="165">
+      <c r="M34" s="178"/>
+      <c r="N34" s="160">
         <f t="shared" si="4"/>
         <v>7200.22</v>
       </c>
-      <c r="O34" s="58"/>
-      <c r="P34" s="59">
+      <c r="O34" s="57"/>
+      <c r="P34" s="58">
         <f t="shared" si="6"/>
         <v>7416.22</v>
       </c>
-      <c r="Q34" s="30">
+      <c r="Q34" s="29">
         <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="45">
+      <c r="A35" s="44">
         <v>23</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D35" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="54">
+      <c r="E35" s="53">
         <v>0.3</v>
       </c>
-      <c r="F35" s="62">
+      <c r="F35" s="61">
         <v>6600.23</v>
       </c>
-      <c r="G35" s="56">
+      <c r="G35" s="55">
         <f>F35</f>
         <v>6600.23</v>
       </c>
-      <c r="H35" s="57">
+      <c r="H35" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="57">
+      <c r="I35" s="56">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="107">
+      <c r="J35" s="106">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="K35" s="107">
+      <c r="K35" s="106">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="166">
+      <c r="L35" s="161">
         <f>EDESUR!I29</f>
         <v>0</v>
       </c>
-      <c r="M35" s="183"/>
-      <c r="N35" s="165">
+      <c r="M35" s="178"/>
+      <c r="N35" s="160">
         <f t="shared" si="4"/>
         <v>7200.23</v>
       </c>
-      <c r="O35" s="64"/>
-      <c r="P35" s="59">
+      <c r="O35" s="63"/>
+      <c r="P35" s="58">
         <f t="shared" si="6"/>
         <v>7416.23</v>
       </c>
-      <c r="Q35" s="30">
+      <c r="Q35" s="29">
         <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="65"/>
-      <c r="B36" s="65"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="119">
+      <c r="A36" s="64"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="114">
         <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="38">
         <f>SUM(F13:F35)</f>
         <v>2348836.7600000012</v>
       </c>
-      <c r="G36" s="43">
+      <c r="G36" s="42">
         <f>SUM(G13:G35)</f>
-        <v>2504691.1700000009</v>
-      </c>
-      <c r="H36" s="43">
+        <v>2511489.3800000008</v>
+      </c>
+      <c r="H36" s="42">
         <f>SUM(H13:H35)</f>
-        <v>-155854.41</v>
-      </c>
-      <c r="I36" s="43">
+        <v>-162652.62</v>
+      </c>
+      <c r="I36" s="42">
         <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
-        <v>594.0228000000003</v>
-      </c>
-      <c r="J36" s="93">
+        <v>396.01650000000029</v>
+      </c>
+      <c r="J36" s="92">
         <f t="shared" si="11"/>
         <v>2400000</v>
       </c>
-      <c r="K36" s="43">
+      <c r="K36" s="42">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L36" s="67">
+      <c r="L36" s="66">
         <f>SUM(L13:L35)</f>
         <v>103227.02696710824</v>
       </c>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67">
+      <c r="M36" s="66"/>
+      <c r="N36" s="66">
         <f>SUM(N13:N35)</f>
-        <v>2397968.7600000012</v>
-      </c>
-      <c r="O36" s="67">
+        <v>2340972.7600000012</v>
+      </c>
+      <c r="O36" s="66">
         <f t="shared" si="11"/>
-        <v>2481216.7100000009</v>
-      </c>
-      <c r="P36" s="67">
+        <v>2428216.7100000009</v>
+      </c>
+      <c r="P36" s="66">
         <f>SUM(P13:P35)</f>
-        <v>2469906.7600000012</v>
+        <v>2411200.7600000012</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="203" t="str">
+      <c r="C39" s="201" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="203"/>
-      <c r="E39" s="203"/>
-      <c r="F39" s="203"/>
-      <c r="G39" s="203"/>
-      <c r="H39" s="203"/>
-      <c r="I39" s="203"/>
-      <c r="J39" s="203"/>
-      <c r="K39" s="203"/>
-      <c r="L39" s="203"/>
-      <c r="M39" s="203"/>
-      <c r="N39" s="203"/>
+      <c r="D39" s="201"/>
+      <c r="E39" s="201"/>
+      <c r="F39" s="201"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="201"/>
+      <c r="I39" s="201"/>
+      <c r="J39" s="201"/>
+      <c r="K39" s="201"/>
+      <c r="L39" s="201"/>
+      <c r="M39" s="201"/>
+      <c r="N39" s="201"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="203"/>
-      <c r="D40" s="203"/>
-      <c r="E40" s="203"/>
-      <c r="F40" s="203"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="203"/>
-      <c r="I40" s="203"/>
-      <c r="J40" s="203"/>
-      <c r="K40" s="203"/>
-      <c r="L40" s="203"/>
-      <c r="M40" s="203"/>
-      <c r="N40" s="203"/>
+      <c r="C40" s="201"/>
+      <c r="D40" s="201"/>
+      <c r="E40" s="201"/>
+      <c r="F40" s="201"/>
+      <c r="G40" s="201"/>
+      <c r="H40" s="201"/>
+      <c r="I40" s="201"/>
+      <c r="J40" s="201"/>
+      <c r="K40" s="201"/>
+      <c r="L40" s="201"/>
+      <c r="M40" s="201"/>
+      <c r="N40" s="201"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="203"/>
-      <c r="D41" s="203"/>
-      <c r="E41" s="203"/>
-      <c r="F41" s="203"/>
-      <c r="G41" s="203"/>
-      <c r="H41" s="203"/>
-      <c r="I41" s="203"/>
-      <c r="J41" s="203"/>
-      <c r="K41" s="203"/>
-      <c r="L41" s="203"/>
-      <c r="M41" s="203"/>
-      <c r="N41" s="203"/>
+      <c r="C41" s="201"/>
+      <c r="D41" s="201"/>
+      <c r="E41" s="201"/>
+      <c r="F41" s="201"/>
+      <c r="G41" s="201"/>
+      <c r="H41" s="201"/>
+      <c r="I41" s="201"/>
+      <c r="J41" s="201"/>
+      <c r="K41" s="201"/>
+      <c r="L41" s="201"/>
+      <c r="M41" s="201"/>
+      <c r="N41" s="201"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="203"/>
-      <c r="D42" s="203"/>
-      <c r="E42" s="203"/>
-      <c r="F42" s="203"/>
-      <c r="G42" s="203"/>
-      <c r="H42" s="203"/>
-      <c r="I42" s="203"/>
-      <c r="J42" s="203"/>
-      <c r="K42" s="203"/>
-      <c r="L42" s="203"/>
-      <c r="M42" s="203"/>
-      <c r="N42" s="203"/>
+      <c r="C42" s="201"/>
+      <c r="D42" s="201"/>
+      <c r="E42" s="201"/>
+      <c r="F42" s="201"/>
+      <c r="G42" s="201"/>
+      <c r="H42" s="201"/>
+      <c r="I42" s="201"/>
+      <c r="J42" s="201"/>
+      <c r="K42" s="201"/>
+      <c r="L42" s="201"/>
+      <c r="M42" s="201"/>
+      <c r="N42" s="201"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="203"/>
-      <c r="D43" s="203"/>
-      <c r="E43" s="203"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="203"/>
-      <c r="I43" s="203"/>
-      <c r="J43" s="203"/>
-      <c r="K43" s="203"/>
-      <c r="L43" s="203"/>
-      <c r="M43" s="203"/>
-      <c r="N43" s="203"/>
+      <c r="C43" s="201"/>
+      <c r="D43" s="201"/>
+      <c r="E43" s="201"/>
+      <c r="F43" s="201"/>
+      <c r="G43" s="201"/>
+      <c r="H43" s="201"/>
+      <c r="I43" s="201"/>
+      <c r="J43" s="201"/>
+      <c r="K43" s="201"/>
+      <c r="L43" s="201"/>
+      <c r="M43" s="201"/>
+      <c r="N43" s="201"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="203"/>
-      <c r="D44" s="203"/>
-      <c r="E44" s="203"/>
-      <c r="F44" s="203"/>
-      <c r="G44" s="203"/>
-      <c r="H44" s="203"/>
-      <c r="I44" s="203"/>
-      <c r="J44" s="203"/>
-      <c r="K44" s="203"/>
-      <c r="L44" s="203"/>
-      <c r="M44" s="203"/>
-      <c r="N44" s="203"/>
+      <c r="C44" s="201"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="201"/>
+      <c r="G44" s="201"/>
+      <c r="H44" s="201"/>
+      <c r="I44" s="201"/>
+      <c r="J44" s="201"/>
+      <c r="K44" s="201"/>
+      <c r="L44" s="201"/>
+      <c r="M44" s="201"/>
+      <c r="N44" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4679,570 +4726,570 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="125" t="s">
+      <c r="C3" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="127" t="s">
+      <c r="E3" s="122" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="156" t="s">
-        <v>129</v>
-      </c>
-      <c r="I3" s="234" t="s">
+      <c r="G3" s="151" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="235"/>
+      <c r="J3" s="233"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="G4" s="128"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="235"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="G4" s="123"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="233"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="125">
+      <c r="B5" s="120">
         <v>1</v>
       </c>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="192">
+      <c r="E5" s="180">
         <v>12046.778334087237</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="193">
+      <c r="G5" s="181">
         <v>12046.778334087237</v>
       </c>
-      <c r="I5" s="232">
+      <c r="I5" s="230">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="233"/>
+      <c r="J5" s="231"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="125">
+      <c r="B6" s="120">
         <v>1</v>
       </c>
-      <c r="C6" s="125" t="s">
+      <c r="C6" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="192">
+      <c r="E6" s="180">
         <v>31125.624497318255</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="193">
-        <v>0</v>
-      </c>
-      <c r="I6" s="232">
+      <c r="G6" s="181">
+        <v>0</v>
+      </c>
+      <c r="I6" s="230">
         <f t="shared" ref="I6:I19" si="0">E6-G6</f>
         <v>31125.624497318255</v>
       </c>
-      <c r="J6" s="233"/>
+      <c r="J6" s="231"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="125">
+      <c r="B7" s="120">
         <v>1</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="C7" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="192">
+      <c r="E7" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="193">
-        <v>0</v>
-      </c>
-      <c r="I7" s="232">
+      <c r="G7" s="181">
+        <v>0</v>
+      </c>
+      <c r="I7" s="230">
         <f t="shared" si="0"/>
         <v>5421.0502503392572</v>
       </c>
-      <c r="J7" s="233"/>
+      <c r="J7" s="231"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="125">
+      <c r="B8" s="120">
         <v>2</v>
       </c>
-      <c r="C8" s="125" t="s">
+      <c r="C8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="192">
+      <c r="E8" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="193">
+      <c r="G8" s="181">
         <v>5421.0502503392572</v>
       </c>
-      <c r="I8" s="232">
+      <c r="I8" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="233"/>
+      <c r="J8" s="231"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="126">
+      <c r="B9" s="121">
         <v>2</v>
       </c>
-      <c r="C9" s="126" t="s">
+      <c r="C9" s="121" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="192">
+      <c r="E9" s="180">
         <v>6625.7280837479811</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="193">
+      <c r="G9" s="181">
         <v>6625.7280837479811</v>
       </c>
-      <c r="I9" s="232">
+      <c r="I9" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="233"/>
+      <c r="J9" s="231"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="126">
+      <c r="B10" s="121">
         <v>2</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="192">
+      <c r="E10" s="180">
         <v>6625.7280837479811</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="193">
+      <c r="G10" s="181">
         <v>6625.7280837479811</v>
       </c>
-      <c r="I10" s="232">
+      <c r="I10" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="233"/>
+      <c r="J10" s="231"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="126">
+      <c r="B11" s="121">
         <v>2</v>
       </c>
-      <c r="C11" s="126" t="s">
+      <c r="C11" s="121" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="192">
+      <c r="E11" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="193">
+      <c r="G11" s="181">
         <v>5421.0502503392572</v>
       </c>
-      <c r="I11" s="232">
+      <c r="I11" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="233"/>
+      <c r="J11" s="231"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="126">
+      <c r="B12" s="121">
         <v>3</v>
       </c>
-      <c r="C12" s="126" t="s">
+      <c r="C12" s="121" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="192">
+      <c r="E12" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="193">
+      <c r="G12" s="181">
         <v>5421.0502503392572</v>
       </c>
-      <c r="I12" s="232">
+      <c r="I12" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="233"/>
+      <c r="J12" s="231"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="125">
+      <c r="B13" s="120">
         <v>3</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="C13" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="192">
+      <c r="E13" s="180">
         <v>66680.352219450724</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="193">
-        <v>0</v>
-      </c>
-      <c r="I13" s="232">
+      <c r="G13" s="181">
+        <v>0</v>
+      </c>
+      <c r="I13" s="230">
         <f t="shared" si="0"/>
         <v>66680.352219450724</v>
       </c>
-      <c r="J13" s="233"/>
+      <c r="J13" s="231"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="126">
+      <c r="B14" s="121">
         <v>3</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="192">
+      <c r="E14" s="180">
         <v>6625.7280837479811</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="193">
+      <c r="G14" s="181">
         <v>6625.7280837479811</v>
       </c>
-      <c r="I14" s="232">
+      <c r="I14" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="233"/>
+      <c r="J14" s="231"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="126">
+      <c r="B15" s="121">
         <v>3</v>
       </c>
-      <c r="C15" s="126" t="s">
+      <c r="C15" s="121" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="192">
+      <c r="E15" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="193">
+      <c r="G15" s="181">
         <v>5421.0502503392572</v>
       </c>
-      <c r="I15" s="232">
+      <c r="I15" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="233"/>
+      <c r="J15" s="231"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="125">
+      <c r="B16" s="120">
         <v>4</v>
       </c>
-      <c r="C16" s="125" t="s">
+      <c r="C16" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="192">
+      <c r="E16" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="193">
+      <c r="G16" s="181">
         <v>5421.0502503392572</v>
       </c>
-      <c r="I16" s="232">
+      <c r="I16" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="233"/>
+      <c r="J16" s="231"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="126">
+      <c r="B17" s="121">
         <v>4</v>
       </c>
-      <c r="C17" s="126" t="s">
+      <c r="C17" s="121" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="192">
+      <c r="E17" s="180">
         <v>6625.7280837479811</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="193">
+      <c r="G17" s="181">
         <v>6625.7280837479811</v>
       </c>
-      <c r="I17" s="232">
+      <c r="I17" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="233"/>
+      <c r="J17" s="231"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="125">
+      <c r="B18" s="120">
         <v>4</v>
       </c>
-      <c r="C18" s="125" t="s">
+      <c r="C18" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="192">
+      <c r="E18" s="180">
         <v>6625.7280837479811</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="193">
+      <c r="G18" s="181">
         <v>6625.7280837479811</v>
       </c>
-      <c r="I18" s="232">
+      <c r="I18" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="233"/>
+      <c r="J18" s="231"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="126">
+      <c r="B19" s="121">
         <v>4</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="121" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="192">
+      <c r="E19" s="180">
         <v>5421.0502503392572</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="193">
+      <c r="G19" s="181">
         <v>5421.0502503392572</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="230">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="233"/>
+      <c r="J19" s="231"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="G20" s="128"/>
-      <c r="I20" s="232"/>
-      <c r="J20" s="233"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="G20" s="123"/>
+      <c r="I20" s="230"/>
+      <c r="J20" s="231"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="149" t="s">
+      <c r="B21" s="144" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="149"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="151">
+      <c r="C21" s="144"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="146">
         <f>SUM(E5:E20)</f>
         <v>180928.74722197096</v>
       </c>
-      <c r="F21" s="152"/>
-      <c r="G21" s="151">
+      <c r="F21" s="147"/>
+      <c r="G21" s="146">
         <f>SUM(G5:G20)</f>
         <v>77701.720254862681</v>
       </c>
-      <c r="I21" s="232">
+      <c r="I21" s="230">
         <f>E21-G21</f>
         <v>103227.02696710828</v>
       </c>
-      <c r="J21" s="233"/>
+      <c r="J21" s="231"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="125" t="s">
+      <c r="B22" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="125">
+      <c r="C22" s="120">
         <v>1</v>
       </c>
-      <c r="E22" s="194">
+      <c r="E22" s="182">
         <v>702.72873615508888</v>
       </c>
-      <c r="G22" s="133">
+      <c r="G22" s="128">
         <f>E22</f>
         <v>702.72873615508888</v>
       </c>
-      <c r="I22" s="232">
+      <c r="I22" s="230">
         <f t="shared" ref="I22" si="1">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="233"/>
+      <c r="J22" s="231"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="125" t="s">
+      <c r="B23" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="125">
+      <c r="C23" s="120">
         <v>2</v>
       </c>
-      <c r="E23" s="194">
+      <c r="E23" s="182">
         <v>602.33891670436185</v>
       </c>
-      <c r="G23" s="133">
+      <c r="G23" s="128">
         <f t="shared" ref="G23:G29" si="2">E23</f>
         <v>602.33891670436185</v>
       </c>
-      <c r="I23" s="232">
+      <c r="I23" s="230">
         <f t="shared" ref="I23:I31" si="3">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="233"/>
+      <c r="J23" s="231"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="125" t="s">
+      <c r="B24" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="125">
+      <c r="C24" s="120">
         <v>3</v>
       </c>
-      <c r="E24" s="194">
+      <c r="E24" s="182">
         <v>602.33891670436185</v>
       </c>
-      <c r="G24" s="133">
+      <c r="G24" s="128">
         <f t="shared" si="2"/>
         <v>602.33891670436185</v>
       </c>
-      <c r="I24" s="232">
+      <c r="I24" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="233"/>
+      <c r="J24" s="231"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="125" t="s">
+      <c r="B25" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="125">
+      <c r="C25" s="120">
         <v>4</v>
       </c>
-      <c r="E25" s="194">
+      <c r="E25" s="182">
         <v>602.33891670436185</v>
       </c>
-      <c r="G25" s="133">
+      <c r="G25" s="128">
         <f t="shared" si="2"/>
         <v>602.33891670436185</v>
       </c>
-      <c r="I25" s="232">
+      <c r="I25" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="233"/>
+      <c r="J25" s="231"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="125" t="s">
+      <c r="B26" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="125">
+      <c r="C26" s="120">
         <v>5</v>
       </c>
-      <c r="E26" s="194">
+      <c r="E26" s="182">
         <v>602.33891670436185</v>
       </c>
-      <c r="G26" s="133">
+      <c r="G26" s="128">
         <f t="shared" si="2"/>
         <v>602.33891670436185</v>
       </c>
-      <c r="I26" s="232">
+      <c r="I26" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="233"/>
+      <c r="J26" s="231"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="125">
+      <c r="C27" s="120">
         <v>6</v>
       </c>
-      <c r="E27" s="194">
+      <c r="E27" s="182">
         <v>301.16945835218092</v>
       </c>
-      <c r="G27" s="133">
+      <c r="G27" s="128">
         <f t="shared" si="2"/>
         <v>301.16945835218092</v>
       </c>
-      <c r="I27" s="232">
+      <c r="I27" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="233"/>
+      <c r="J27" s="231"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="125" t="s">
+      <c r="B28" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="125">
+      <c r="C28" s="120">
         <v>7</v>
       </c>
-      <c r="E28" s="194">
+      <c r="E28" s="182">
         <v>301.16945835218092</v>
       </c>
-      <c r="G28" s="133">
+      <c r="G28" s="128">
         <f t="shared" si="2"/>
         <v>301.16945835218092</v>
       </c>
-      <c r="I28" s="232">
+      <c r="I28" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="233"/>
+      <c r="J28" s="231"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="125" t="s">
+      <c r="B29" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="125">
+      <c r="C29" s="120">
         <v>8</v>
       </c>
-      <c r="E29" s="194">
+      <c r="E29" s="182">
         <v>301.16945835218092</v>
       </c>
-      <c r="G29" s="133">
+      <c r="G29" s="128">
         <f t="shared" si="2"/>
         <v>301.16945835218092</v>
       </c>
-      <c r="I29" s="232">
+      <c r="I29" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="233"/>
+      <c r="J29" s="231"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="154" t="s">
+      <c r="B30" s="149" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="155"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="151">
+      <c r="C30" s="150"/>
+      <c r="D30" s="148"/>
+      <c r="E30" s="146">
         <f>SUM(E22:E29)</f>
         <v>4015.592778029079</v>
       </c>
-      <c r="F30" s="153"/>
-      <c r="G30" s="151">
+      <c r="F30" s="148"/>
+      <c r="G30" s="146">
         <f>SUM(G22:G29)</f>
         <v>4015.592778029079</v>
       </c>
-      <c r="I30" s="232">
+      <c r="I30" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="233"/>
+      <c r="J30" s="231"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E31" s="132"/>
-      <c r="G31" s="129"/>
-      <c r="I31" s="232">
+      <c r="E31" s="127"/>
+      <c r="G31" s="124"/>
+      <c r="I31" s="230">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="233"/>
+      <c r="J31" s="231"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E32" s="130"/>
-      <c r="G32" s="131"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="233"/>
+      <c r="E32" s="125"/>
+      <c r="G32" s="126"/>
+      <c r="I32" s="230"/>
+      <c r="J32" s="231"/>
     </row>
     <row r="33" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E33" s="132">
+      <c r="E33" s="127">
         <f>E30+E21</f>
         <v>184944.34000000003</v>
       </c>
-      <c r="G33" s="129">
+      <c r="G33" s="124">
         <f>G21+G30</f>
         <v>81717.313032891761</v>
       </c>
-      <c r="I33" s="232">
+      <c r="I33" s="230">
         <f>E33-G33</f>
         <v>103227.02696710826</v>
       </c>
-      <c r="J33" s="233"/>
+      <c r="J33" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="31">
